--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PAPALOTE TJ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PAPALOTE TJ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC77"/>
+  <dimension ref="A1:AC81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,12 +713,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>215094</t>
+          <t>99864</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>97619</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BRAYAN ULISES</t>
+          <t xml:space="preserve">JULIETA </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAYORQUIN </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t xml:space="preserve">CERON </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,28 +748,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6646148601</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6641845462</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C. LOS ALAMOS </t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>10-08-2008</t>
+          <t>10-06-1985</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MAYORQUINBRYAN0@GMAIL.COM</t>
+          <t>JULIETA.SCERON@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>15-01-2024 19:17:18</t>
+          <t>13-06-2022 18:37:21</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -779,36 +783,44 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-02-2026 21:04:57</t>
+          <t>19-02-2026 09:01:43</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>19-02-2026 08:59:02</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -816,36 +828,44 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26120522058650005224</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>26070522489770003735</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>206348</t>
+          <t>215094</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,17 +875,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SILVIA</t>
+          <t>BRAYAN ULISES</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t xml:space="preserve">MAYORQUIN </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -875,28 +895,28 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6641695831</t>
+          <t>6646148601</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>02-01-1988</t>
+          <t>10-08-2008</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>SILVIA_RUIZPEREZ@HOTMAIL.COM</t>
+          <t>MAYORQUINBRYAN0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>13-11-2023 17:28:40</t>
+          <t>15-01-2024 19:17:18</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -911,22 +931,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>09-02-2026 19:33:12</t>
+          <t>03-02-2026 21:04:57</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -943,14 +963,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26070522211180003005</t>
+          <t>26120522058650005224</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -967,12 +987,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>99864</t>
+          <t>206348</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>97619</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -982,17 +1002,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JULIETA </t>
+          <t>SILVIA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERON </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1002,14 +1022,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6641845462</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C. LOS ALAMOS </t>
-        </is>
-      </c>
+          <t>6641695831</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1017,17 +1033,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10-06-1985</t>
+          <t>02-01-1988</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>JULIETA.SCERON@GMAIL.COM</t>
+          <t>SILVIA_RUIZPEREZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>13-06-2022 18:37:21</t>
+          <t>13-11-2023 17:28:40</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1037,44 +1053,36 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>19-02-2026 09:01:43</t>
+          <t>09-02-2026 19:33:12</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>19-02-2026 08:59:02</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1082,32 +1090,24 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26070522489770003735</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>TOMAS HERNANDEZ MARTINEZ</t>
-        </is>
-      </c>
+          <t>26070522211180003005</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2754,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>340176</t>
+          <t>306149</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17994</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2769,17 +2769,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LEOBARDO</t>
+          <t>CLAUDIA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LEAL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>OLIVA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2789,32 +2789,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6652803978</t>
+          <t>6641145151</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18-10-1970</t>
+          <t>02-01-1978</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>LGARCIAJ@EDUBC.COM.MX</t>
+          <t>KLAUDYAJB02@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-02-2026 14:31:22</t>
+          <t>28-07-2025 07:56:57</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-02-2026 14:34:05</t>
+          <t>11-02-2026 18:12:09</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>02-02-2026 14:33:25</t>
+          <t>10-02-2026 17:41:41</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2865,10 +2865,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26070522013020002374</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
+          <t>26070522273440003207</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2877,24 +2881,24 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>306149</t>
+          <t>340176</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>17994</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2904,17 +2908,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CLAUDIA</t>
+          <t>LEOBARDO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LEAL</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OLIVA</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2924,32 +2928,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6641145151</t>
+          <t>6652803978</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>02-01-1978</t>
+          <t>18-10-1970</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>KLAUDYAJB02@GMAIL.COM</t>
+          <t>LGARCIAJ@EDUBC.COM.MX</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>28-07-2025 07:56:57</t>
+          <t>02-02-2026 14:31:22</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2960,7 +2964,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2970,17 +2974,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>11-02-2026 18:12:09</t>
+          <t>02-02-2026 14:34:05</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>10-02-2026 17:41:41</t>
+          <t>02-02-2026 14:33:25</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3000,14 +3004,10 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26070522273440003207</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26070522013020002374</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
@@ -3016,12 +3016,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -3163,12 +3163,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>341175</t>
+          <t>341841</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18993</t>
+          <t>19659</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3178,17 +3178,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BRIANA TERESA</t>
+          <t xml:space="preserve">ALEXIA </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEA </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GALINDO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6645681580</t>
+          <t>2295094042</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>REF</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3213,17 +3213,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>29-10-2011</t>
+          <t>01-06-1998</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BRIANA.VEAS@ICLOUD.COM</t>
+          <t>ALEGAL.1298@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>04-02-2026 19:34:05</t>
+          <t>07-02-2026 14:32:28</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3244,17 +3244,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-02-2026 19:36:22</t>
+          <t>07-02-2026 14:36:05</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>04-02-2026 19:35:54</t>
+          <t>07-02-2026 14:35:29</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26070522088290002649</t>
+          <t>26070522162160002873</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3298,12 +3298,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>341319</t>
+          <t>340696</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3313,17 +3313,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARCOS URIEL </t>
+          <t>ANA JOSELYN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDRANO </t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOTO </t>
+          <t>ARIPEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3333,28 +3333,28 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6861440207</t>
+          <t>6643624758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>04-05-2011</t>
+          <t>09-04-2001</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MARCOSURIELMEDRANOSOTO9@GMAIL.COM</t>
+          <t>ANNAVAZQUEZ04@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>05-02-2026 14:13:10</t>
+          <t>03-02-2026 17:01:07</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3369,22 +3369,22 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>05-02-2026 14:15:00</t>
+          <t>03-02-2026 17:02:58</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>03-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -3401,19 +3401,19 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26070522106310002690</t>
+          <t>26070522047750002488</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>340696</t>
+          <t>341175</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18514</t>
+          <t>18993</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3567,17 +3567,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ANA JOSELYN</t>
+          <t>BRIANA TERESA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t xml:space="preserve">VEA </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ARIPEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3587,10 +3587,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6643624758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>6645681580</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3598,56 +3602,60 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>09-04-2001</t>
+          <t>29-10-2011</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ANNAVAZQUEZ04@GMAIL.COM</t>
+          <t>BRIANA.VEAS@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>03-02-2026 17:01:07</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 19:34:05</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>03-02-2026 17:02:58</t>
+          <t>04-02-2026 19:36:22</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>04-02-2026 19:35:54</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3655,14 +3663,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26070522047750002488</t>
+          <t>26070522088290002649</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3679,12 +3687,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>340893</t>
+          <t>341319</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18711</t>
+          <t>19137</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3694,17 +3702,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PRISILA</t>
+          <t xml:space="preserve">MARCOS URIEL </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t xml:space="preserve">MEDRANO </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t xml:space="preserve">SOTO </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3714,75 +3722,67 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6645204741</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>PRIV TEQUESQUITENGO 204</t>
-        </is>
-      </c>
+          <t>6861440207</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>05-02-1997</t>
+          <t>04-05-2011</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>KITTYPEACE1@HOTMAIL.COM</t>
+          <t>MARCOSURIELMEDRANOSOTO9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>04-02-2026 08:27:45</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>05-02-2026 14:13:10</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>04-02-2026 08:37:12</t>
+          <t>05-02-2026 14:15:00</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>04-02-2026 08:32:48</t>
-        </is>
-      </c>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3790,19 +3790,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26070522069700002552</t>
+          <t>26070522106310002690</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3814,12 +3814,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>265498</t>
+          <t>340893</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>63002</t>
+          <t>18711</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3829,52 +3829,52 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JAZMIN</t>
+          <t>PRISILA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MARCIAL</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6199397939</t>
+          <t>6645204741</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5RF</t>
+          <t>PRIV TEQUESQUITENGO 204</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>03-03-1997</t>
+          <t>05-02-1997</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>JAZMIN603163@GMAIL.COM</t>
+          <t>KITTYPEACE1@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10-11-2024 23:41:22</t>
+          <t>04-02-2026 08:27:45</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3895,17 +3895,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>09-02-2026 19:05:18</t>
+          <t>04-02-2026 08:37:12</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>09-02-2026 19:04:43</t>
+          <t>04-02-2026 08:32:48</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3925,14 +3925,10 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26070522209500002998</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26070522069700002552</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3941,7 +3937,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Jesus Alejandro  Partida Partida</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3953,12 +3949,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>341841</t>
+          <t>265498</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19659</t>
+          <t>63002</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3968,52 +3964,52 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEXIA </t>
+          <t>JAZMIN</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GALINDO</t>
+          <t>MARCIAL</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2295094042</t>
+          <t>6199397939</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>5RF</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>01-06-1998</t>
+          <t>03-03-1997</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ALEGAL.1298@GMAIL.COM</t>
+          <t>JAZMIN603163@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>07-02-2026 14:32:28</t>
+          <t>10-11-2024 23:41:22</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4034,17 +4030,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>07-02-2026 14:36:05</t>
+          <t>09-02-2026 19:05:18</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>07-02-2026 14:35:29</t>
+          <t>09-02-2026 19:04:43</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4064,10 +4060,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26070522162160002873</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
+          <t>26070522209500002998</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Jesus Alejandro  Partida Partida</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4088,12 +4088,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>341892</t>
+          <t>315330</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4103,17 +4103,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JUANA MARIA</t>
+          <t>LESLIE MAYBEL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>LANDEROS</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6647297856</t>
+          <t>6641890047</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4134,17 +4134,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>12-07-1978</t>
+          <t>04-09-1998</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>PENDIENTE.JUANA@GMAIL.COM</t>
+          <t>MAYBEL.MYCH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>08-02-2026 10:02:26</t>
+          <t>22-09-2025 17:31:56</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4159,28 +4159,28 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>08-02-2026 10:04:29</t>
+          <t>23-02-2026 19:54:12</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V28" t="inlineStr"/>
@@ -4191,36 +4191,36 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26070522169130002878</t>
+          <t>26070522600750003966</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342125</t>
+          <t>341892</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19943</t>
+          <t>19710</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4230,17 +4230,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KATHERINE NEVRASKA</t>
+          <t>JUANA MARIA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>COVARRUBIAS</t>
+          <t>LANDEROS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4250,14 +4250,10 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6647136178</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>C CABO VIRGENES 165</t>
-        </is>
-      </c>
+          <t>6647297856</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4265,60 +4261,56 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>29-04-2004</t>
+          <t>12-07-1978</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>KTYSANTIAGO2004@GMAIL.COM</t>
+          <t>PENDIENTE.JUANA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-02-2026 11:58:38</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>08-02-2026 10:02:26</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>09-02-2026 12:24:20</t>
+          <t>08-02-2026 10:04:29</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>09-02-2026 12:23:02</t>
-        </is>
-      </c>
+          <t>08-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4326,23 +4318,19 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26070522190300002931</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26070522169130002878</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Jesus Alejandro  Partida Partida</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4354,12 +4342,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>340004</t>
+          <t>342125</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17822</t>
+          <t>19943</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4369,17 +4357,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EZEQUIEL</t>
+          <t>KATHERINE NEVRASKA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GASTELUM</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MÉNDEZ</t>
+          <t>COVARRUBIAS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4389,67 +4377,75 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6645318296</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6647136178</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>C CABO VIRGENES 165</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>02-07-2007</t>
+          <t>29-04-2004</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>EZEQUIELGASTELUM2@GMAIL.COM</t>
+          <t>KTYSANTIAGO2004@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>02-02-2026 10:18:49</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 11:58:38</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>02-02-2026 10:26:32</t>
+          <t>09-02-2026 12:24:20</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>09-02-2026 12:23:02</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4457,19 +4453,23 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26070522004870002347</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr"/>
+          <t>26070522190300002931</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Jesus Alejandro  Partida Partida</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4481,12 +4481,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342214</t>
+          <t>340179</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR EDUARDO </t>
+          <t>JUAN ANTONIO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>URIARTE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6641272476</t>
+          <t>6291079920</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DAS</t>
+          <t>JFHF</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4531,17 +4531,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>07-11-2005</t>
+          <t>18-01-2007</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>EL7615132@GMAIL.COM</t>
+          <t>JUANMURILLOU@EDUBC.COM.MX</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-02-2026 15:32:17</t>
+          <t>02-02-2026 14:35:17</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4562,17 +4562,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>09-02-2026 15:34:55</t>
+          <t>02-02-2026 14:38:10</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>09-02-2026 15:34:41</t>
+          <t>02-02-2026 14:37:37</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26070522195720002961</t>
+          <t>26070522013130002376</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4604,24 +4604,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>340179</t>
+          <t>342214</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4631,17 +4631,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JUAN ANTONIO</t>
+          <t xml:space="preserve">VICTOR EDUARDO </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>URIARTE</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6291079920</t>
+          <t>6641272476</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>JFHF</t>
+          <t>DAS</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4666,17 +4666,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18-01-2007</t>
+          <t>07-11-2005</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>JUANMURILLOU@EDUBC.COM.MX</t>
+          <t>EL7615132@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>02-02-2026 14:35:17</t>
+          <t>09-02-2026 15:32:17</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -4697,17 +4697,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>02-02-2026 14:38:10</t>
+          <t>09-02-2026 15:34:55</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>02-02-2026 14:37:37</t>
+          <t>09-02-2026 15:34:41</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26070522013130002376</t>
+          <t>26070522195720002961</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -5148,12 +5148,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>340699</t>
+          <t>340704</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5163,17 +5163,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NOE ALEJANDRO</t>
+          <t>ALMA JUDITH</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>MARTÍNEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5183,10 +5183,14 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6631565587</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>6631064684</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5194,56 +5198,60 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>13-09-2001</t>
+          <t>08-12-1987</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>TNAMELESS9@GMAIL.COM</t>
+          <t>ALMITA2015.ABE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>03-02-2026 17:04:19</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 17:09:20</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>03-02-2026 17:06:08</t>
+          <t>10-02-2026 17:21:55</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>10-02-2026 17:21:14</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5251,14 +5259,18 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26070522047920002489</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
+          <t>26070522239480003099</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5275,12 +5287,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>342475</t>
+          <t>340004</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5290,17 +5302,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA JULIA </t>
+          <t>EZEQUIEL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>GASTELUM</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MÉNDEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5310,75 +5322,67 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6643714693</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
+          <t>6645318296</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>07-12-1985</t>
+          <t>02-07-2007</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>AVILAJULIA746@GMAIL.COM</t>
+          <t>EZEQUIELGASTELUM2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>09-02-2026 20:08:38</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>02-02-2026 10:18:49</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>09-02-2026 20:10:52</t>
+          <t>02-02-2026 10:26:32</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>09-02-2026 20:10:24</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5386,19 +5390,19 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26070522213060003014</t>
+          <t>26070522004870002347</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5410,12 +5414,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>340910</t>
+          <t>342475</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5425,32 +5429,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ANA</t>
+          <t xml:space="preserve">ANA JULIA </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6195302607</t>
+          <t>6643714693</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AV DE CHAPALA 4635 COL EL LAGO</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5460,17 +5464,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>09-06-1995</t>
+          <t>07-12-1985</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ANAELSACARBAJAL84@GMAIL.COM</t>
+          <t>AVILAJULIA746@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>04-02-2026 09:22:30</t>
+          <t>09-02-2026 20:08:38</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5491,7 +5495,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>09-02-2026 09:58:45</t>
+          <t>09-02-2026 20:10:52</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -5501,7 +5505,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>09-02-2026 09:57:56</t>
+          <t>09-02-2026 20:10:24</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5511,7 +5515,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5521,19 +5525,11 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26070522187140002917</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>TOMAS HERNANDEZ MARTINEZ</t>
-        </is>
-      </c>
+          <t>26070522213060003014</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
           <t>499</t>
@@ -5541,7 +5537,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Jesus Alejandro  Partida Partida</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5553,12 +5549,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>340704</t>
+          <t>340810</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18522</t>
+          <t>18628</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5568,17 +5564,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ALMA JUDITH</t>
+          <t>DANIA GISSEL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MARTÍNEZ</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5588,12 +5584,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6631064684</t>
+          <t>6632070260</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>YUY</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5603,17 +5599,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>08-12-1987</t>
+          <t>16-09-1997</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ALMITA2015.ABE@GMAIL.COM</t>
+          <t>TDNDANIAMENA0321@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>03-02-2026 17:09:20</t>
+          <t>03-02-2026 19:17:52</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5624,7 +5620,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -5634,17 +5630,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>10-02-2026 17:21:55</t>
+          <t>03-02-2026 19:19:54</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>10-02-2026 17:21:14</t>
+          <t>03-02-2026 19:19:41</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5664,14 +5660,10 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26070522239480003099</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26070522055720002525</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
@@ -5680,7 +5672,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5692,12 +5684,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>340810</t>
+          <t>340863</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>18681</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5707,17 +5699,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DANIA GISSEL</t>
+          <t>ANGIE PAOLA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>PELAEZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5727,12 +5719,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6632070260</t>
+          <t>7441284622</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>YUY</t>
+          <t>COL LA LAJA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5742,48 +5734,52 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>16-09-1997</t>
+          <t>03-06-1997</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>TDNDANIAMENA0321@GMAIL.COM</t>
+          <t>ANGIE.PLZ@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>03-02-2026 19:17:52</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>04-02-2026 06:23:44</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>03-02-2026 19:19:54</t>
+          <t>05-02-2026 06:25:32</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>03-02-2026 19:19:41</t>
+          <t>05-02-2026 06:23:59</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5793,7 +5789,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5803,19 +5799,27 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26070522055720002525</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
+          <t>26070522098680002660</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5827,12 +5831,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>340863</t>
+          <t>341172</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18681</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5842,17 +5846,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ANGIE PAOLA</t>
+          <t xml:space="preserve">YAMIL EDEN </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>AVITIA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PELAEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5862,67 +5866,63 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>7441284622</t>
+          <t>6632013605</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COL LA LAJA</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>03-06-1997</t>
+          <t>19-09-2006</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ANGIE.PLZ@OUTLOOK.COM</t>
+          <t>YAMILAVITIA61@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>04-02-2026 06:23:44</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 19:27:23</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>05-02-2026 06:25:32</t>
+          <t>04-02-2026 19:32:29</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>05-02-2026 06:23:59</t>
+          <t>04-02-2026 19:32:02</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5942,27 +5942,19 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26070522098680002660</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>TOMAS HERNANDEZ MARTINEZ</t>
-        </is>
-      </c>
+          <t>26070522088210002648</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5974,12 +5966,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>340534</t>
+          <t>340699</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5989,95 +5981,87 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BENIR ITZEL</t>
+          <t>NOE ALEJANDRO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>NAVARRETE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NEVAREZ</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6631565587</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>13-09-2001</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>TNAMELESS9@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>03-02-2026 17:04:19</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>03-02-2026 17:06:08</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>6197169503</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>C RIO BLANCO 394</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>17-07-2004</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>ITZELNEVARZ@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>03-02-2026 12:00:41</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Forzoso</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>PROMO FEBRERO 12 MESES</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>05-02-2026 12:21:39</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>05-02-2026 12:21:14</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6085,23 +6069,19 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26070522104310002678</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26070522047920002489</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6113,12 +6093,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>341172</t>
+          <t>341225</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>19043</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6128,17 +6108,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">YAMIL EDEN </t>
+          <t>BLANCA EDITH</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AVITIA</t>
+          <t>DOMÍNGUEZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MONDRAGÓN</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6148,32 +6128,32 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6632013605</t>
+          <t>6644725233</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>BALKASH</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>19-09-2006</t>
+          <t>02-02-2002</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>YAMILAVITIA61@GMAIL.COM</t>
+          <t>MONDRAGONBLANCA87@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>04-02-2026 19:27:23</t>
+          <t>05-02-2026 07:42:04</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6194,17 +6174,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>04-02-2026 19:32:29</t>
+          <t>08-02-2026 10:45:59</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>04-02-2026 19:32:02</t>
+          <t>08-02-2026 10:43:52</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6214,7 +6194,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6224,7 +6204,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26070522088210002648</t>
+          <t>26070522169910002880</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6248,12 +6228,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>341225</t>
+          <t>343380</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19043</t>
+          <t>21197</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6263,17 +6243,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BLANCA EDITH</t>
+          <t>GRACIELA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>DOMÍNGUEZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MONDRAGÓN</t>
+          <t xml:space="preserve">PEÑA </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6283,12 +6263,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6644725233</t>
+          <t>6642061015</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>BALKASH</t>
+          <t>CALZ MEDITERRANEO</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6298,17 +6278,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>02-02-2002</t>
+          <t>02-10-1960</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>MONDRAGONBLANCA87@GMAIL.COM</t>
+          <t>GRACIELAHERNANDEZ26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>05-02-2026 07:42:04</t>
+          <t>12-02-2026 18:59:53</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6319,7 +6299,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6329,17 +6309,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>08-02-2026 10:45:59</t>
+          <t>12-02-2026 19:10:56</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>08-02-2026 10:43:52</t>
+          <t>12-02-2026 19:08:55</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6359,7 +6339,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26070522169910002880</t>
+          <t>26070522304190003308</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
@@ -6371,24 +6351,24 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>343380</t>
+          <t>343488</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21197</t>
+          <t>21305</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6398,17 +6378,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GRACIELA</t>
+          <t>EILAN DUVIER ALFREDO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑA </t>
+          <t>PAREDES</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6418,32 +6398,32 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6642061015</t>
+          <t>6645273986</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CALZ MEDITERRANEO</t>
+          <t>C LAGO TOGO 5308 A 303</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>02-10-1960</t>
+          <t>25-11-2012</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>GRACIELAHERNANDEZ26@GMAIL.COM</t>
+          <t>DUVIER.701@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>12-02-2026 18:59:53</t>
+          <t>13-02-2026 12:34:30</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6464,17 +6444,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>12-02-2026 19:10:56</t>
+          <t>13-02-2026 12:48:31</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>12-02-2026 19:08:55</t>
+          <t>13-02-2026 12:47:47</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6494,7 +6474,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26070522304190003308</t>
+          <t>26070522319940003345</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -6518,12 +6498,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>343488</t>
+          <t>340910</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21305</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6533,52 +6513,52 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EILAN DUVIER ALFREDO</t>
+          <t>ANA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PAREDES</t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6645273986</t>
+          <t>6195302607</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>C LAGO TOGO 5308 A 303</t>
+          <t>AV DE CHAPALA 4635 COL EL LAGO</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>25-11-2012</t>
+          <t>09-06-1995</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>DUVIER.701@ICLOUD.COM</t>
+          <t>ANAELSACARBAJAL84@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>13-02-2026 12:34:30</t>
+          <t>04-02-2026 09:22:30</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6599,17 +6579,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>13-02-2026 12:48:31</t>
+          <t>09-02-2026 09:58:45</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>13-02-2026 12:47:47</t>
+          <t>09-02-2026 09:57:56</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6619,7 +6599,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6629,11 +6609,19 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26070522319940003345</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
+          <t>26070522187140002917</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>499</t>
@@ -6641,24 +6629,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alejandro  Partida Partida</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>343112</t>
+          <t>340534</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6668,30 +6656,34 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NAYELY</t>
+          <t>BENIR ITZEL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PELAYO</t>
+          <t>NEVAREZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6865495658</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>6197169503</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>C RIO BLANCO 394</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6699,56 +6691,60 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>13-05-1990</t>
+          <t>17-07-2004</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>NAYELY.JAUREGUI@GMAIL.COM</t>
+          <t>ITZELNEVARZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>11-02-2026 19:01:35</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 12:00:41</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>18-02-2026 18:57:39</t>
+          <t>05-02-2026 12:21:39</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr"/>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>05-02-2026 12:21:14</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6756,36 +6752,40 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26070522473850003704</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr"/>
+          <t>26070522104310002678</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>341542</t>
+          <t>343684</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19360</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>HARAN</t>
+          <t>ROSARIO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOJORQUEZ </t>
+          <t>ONTIVEROS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6815,75 +6815,67 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8121717296</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>ESTANDARTE DE GUADALUPE #7625</t>
-        </is>
-      </c>
+          <t>6647576374</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>30-08-2000</t>
+          <t>23-12-1991</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>MH63638@GMAIL.COM</t>
+          <t>SHARIZ280515@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>06-02-2026 12:27:00</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>14-02-2026 10:11:43</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>06-02-2026 12:27:01</t>
+          <t>14-02-2026 10:13:58</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>06-02-2026 12:27:01</t>
-        </is>
-      </c>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6891,36 +6883,36 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26070522135360002789</t>
+          <t>26070522345600003411</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>341903</t>
+          <t>341842</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19721</t>
+          <t>19660</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6930,17 +6922,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EDGAR OSVALDO</t>
+          <t xml:space="preserve">MARIA SULEMA </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>CUAMATZI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t xml:space="preserve">PUERTO </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6950,32 +6942,32 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6647745824</t>
+          <t>6645281374</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>30-04-2010</t>
+          <t>19-05-2005</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>OFALOFALIN@GMAIL.COM</t>
+          <t>CUAMATZIMARIA1720@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>08-02-2026 10:47:34</t>
+          <t>07-02-2026 14:33:00</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6986,7 +6978,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -6996,17 +6988,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>08-02-2026 10:49:56</t>
+          <t>07-02-2026 14:38:14</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>08-02-2026 10:49:29</t>
+          <t>07-02-2026 14:37:48</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7026,7 +7018,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26070522170000002882</t>
+          <t>26070522162170002874</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -7038,7 +7030,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7050,12 +7042,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>343381</t>
+          <t>341905</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21198</t>
+          <t>19723</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7065,17 +7057,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>IVETTE CYNDEL</t>
+          <t xml:space="preserve">ALIZON </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7085,12 +7077,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6642061023</t>
+          <t>6632243995</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7100,17 +7092,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>02-04-1988</t>
+          <t>14-05-2009</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CYNDEL08@HOTMAIL.COM</t>
+          <t>WAYTOJUNI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>12-02-2026 19:00:09</t>
+          <t>08-02-2026 10:51:13</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -7131,17 +7123,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>12-02-2026 19:13:58</t>
+          <t>08-02-2026 10:53:01</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>12-02-2026 19:13:35</t>
+          <t>08-02-2026 10:52:34</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7161,7 +7153,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26070522304320003309</t>
+          <t>26070522170030002883</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7173,12 +7165,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7443,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>343684</t>
+          <t>343112</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21501</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7466,17 +7458,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ROSARIO</t>
+          <t>NAYELY</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ONTIVEROS</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>PELAYO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7486,7 +7478,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6647576374</t>
+          <t>6865495658</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7497,17 +7489,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>23-12-1991</t>
+          <t>13-05-1990</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>SHARIZ280515@GMAIL.COM</t>
+          <t>NAYELY.JAUREGUI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>14-02-2026 10:11:43</t>
+          <t>11-02-2026 19:01:35</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7522,28 +7514,28 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>14-02-2026 10:13:58</t>
+          <t>18-02-2026 18:57:39</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V53" t="inlineStr"/>
@@ -7554,36 +7546,36 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26070522345600003411</t>
+          <t>26070522473850003704</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>344438</t>
+          <t>343381</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22255</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7593,17 +7585,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ALEXIS</t>
+          <t>IVETTE CYNDEL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>VELA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7613,39 +7605,35 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6634626985</t>
+          <t>6642061023</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>C DIAMANTE 109 5</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>16-08-2000</t>
+          <t>02-04-1988</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>ALEXIS.LOPEZZ1608@GMAIL.COM</t>
+          <t>CYNDEL08@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>17-02-2026 10:10:27</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 19:00:09</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7663,17 +7651,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>17-02-2026 10:19:08</t>
+          <t>12-02-2026 19:13:58</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>17-02-2026 10:16:01</t>
+          <t>12-02-2026 19:13:35</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7693,7 +7681,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26070522423830003542</t>
+          <t>26070522304320003309</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
@@ -7717,12 +7705,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>341842</t>
+          <t>342057</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19660</t>
+          <t>19875</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7732,17 +7720,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA SULEMA </t>
+          <t>FRANCISCO ROSARIO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CUAMATZI</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">PUERTO </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7752,63 +7740,67 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6645281374</t>
+          <t>6871795893</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PORTOFINO 2028 A</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>19-05-2005</t>
+          <t>03-02-1998</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CUAMATZIMARIA1720@GMAIL.COM</t>
+          <t>FRANCISCOHDZ.0298@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>07-02-2026 14:33:00</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>09-02-2026 08:52:27</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>07-02-2026 14:38:14</t>
+          <t>13-02-2026 07:07:01</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>07-02-2026 14:37:48</t>
+          <t>13-02-2026 07:03:42</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7828,14 +7820,18 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26070522162170002874</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr"/>
+          <t>26070522315080003331</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -7852,12 +7848,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>341905</t>
+          <t>342077</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19723</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7867,19 +7863,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALIZON </t>
+          <t>MONICA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>GUTIERREZ</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>DOMINGUEZ</t>
-        </is>
-      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>52</t>
@@ -7887,14 +7883,10 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6632243995</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>RE</t>
-        </is>
-      </c>
+          <t>6643727163</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7902,60 +7894,56 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>14-05-2009</t>
+          <t>23-09-1993</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>WAYTOJUNI@GMAIL.COM</t>
+          <t>MONICA.GTZ939@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>08-02-2026 10:51:13</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>09-02-2026 09:46:37</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>08-02-2026 10:53:01</t>
+          <t>19-02-2026 09:07:04</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>08-02-2026 10:52:34</t>
-        </is>
-      </c>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7963,19 +7951,23 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26070522170030002883</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr"/>
+          <t>26070522489860003737</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7987,12 +7979,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>342057</t>
+          <t>342166</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8002,17 +7994,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FRANCISCO ROSARIO</t>
+          <t>MIA SHERLYN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>VELA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>ALEGRE</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8022,32 +8014,28 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6871795893</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>PORTOFINO 2028 A</t>
-        </is>
-      </c>
+          <t>6647313220</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>03-02-1998</t>
+          <t>07-05-2008</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>FRANCISCOHDZ.0298@GMAIL.COM</t>
+          <t>707MKSZK@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>09-02-2026 08:52:27</t>
+          <t>09-02-2026 13:48:38</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8057,44 +8045,36 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>13-02-2026 07:07:01</t>
+          <t>09-02-2026 13:49:41</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>13-02-2026 07:03:42</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8102,40 +8082,36 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26070522315080003331</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26070522192160002938</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>342077</t>
+          <t>341401</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8145,7 +8121,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MONICA</t>
+          <t>ALONDRA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -8155,7 +8131,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>TREJO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8165,10 +8141,14 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6643727163</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>6647580850</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>C SONORA 4157</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8176,56 +8156,60 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>23-09-1993</t>
+          <t>02-01-1999</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>MONICA.GTZ939@GMAIL.COM</t>
+          <t>AMTZT.02@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>09-02-2026 09:46:37</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 17:38:32</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>19-02-2026 09:07:04</t>
+          <t>07-02-2026 13:16:46</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr"/>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>07-02-2026 13:16:15</t>
+        </is>
+      </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8233,40 +8217,40 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26070522489860003737</t>
+          <t>26070522161600002868</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>341401</t>
+          <t>345666</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19219</t>
+          <t>87831</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8276,17 +8260,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ALONDRA</t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>ARMENTA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TREJO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8296,12 +8280,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6647580850</t>
+          <t>6645204568</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>C SONORA 4157</t>
+          <t>C PUERTO ESCONDIDO 20139</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8311,20 +8295,24 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>02-01-1999</t>
+          <t>02-04-1991</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>AMTZT.02@GMAIL.COM</t>
+          <t>KAR0LINA89@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>05-02-2026 17:38:32</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>23-02-2026 08:05:33</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8342,17 +8330,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>07-02-2026 13:16:46</t>
+          <t>23-02-2026 08:12:41</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>07-02-2026 13:16:15</t>
+          <t>23-02-2026 08:11:48</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8372,14 +8360,10 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26070522161600002868</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26070522573540003894</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
@@ -8400,12 +8384,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>342166</t>
+          <t>341542</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8415,17 +8399,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MIA SHERLYN</t>
+          <t>HARAN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>VELA</t>
+          <t xml:space="preserve">BOJORQUEZ </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ALEGRE</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8435,67 +8419,75 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6647313220</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>8121717296</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>ESTANDARTE DE GUADALUPE #7625</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>07-05-2008</t>
+          <t>30-08-2000</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>707MKSZK@GMAIL.COM</t>
+          <t>MH63638@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>09-02-2026 13:48:38</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>06-02-2026 12:27:00</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>09-02-2026 13:49:41</t>
+          <t>06-02-2026 12:27:01</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr"/>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>06-02-2026 12:27:01</t>
+        </is>
+      </c>
       <c r="U60" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8503,14 +8495,14 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26070522192160002938</t>
+          <t>26070522135360002789</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
@@ -8654,12 +8646,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>341885</t>
+          <t>344438</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19703</t>
+          <t>22255</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8669,17 +8661,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAOMY JARALDY </t>
+          <t>ALEXIS</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MORAILA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>VELA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8689,67 +8681,79 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6642663651</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>6634626985</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>C DIAMANTE 109 5</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>06-07-1999</t>
+          <t>16-08-2000</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>NAOMI.MORAILA@GMAIL.COM</t>
+          <t>ALEXIS.LOPEZZ1608@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>08-02-2026 09:55:33</t>
+          <t>17-02-2026 10:10:27</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>08-02-2026 10:00:42</t>
+          <t>17-02-2026 10:19:08</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>17-02-2026 10:16:01</t>
+        </is>
+      </c>
       <c r="U62" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8757,18 +8761,14 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26070522169030002877</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26070522423830003542</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
@@ -8785,12 +8785,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>344666</t>
+          <t>341885</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22483</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8800,17 +8800,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MARIA DE LOS ANGELES</t>
+          <t xml:space="preserve">NAOMY JARALDY </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARDENAS </t>
+          <t>MORAILA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BUENROSTRO</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8820,14 +8820,10 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6641235751</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>JARDINES</t>
-        </is>
-      </c>
+          <t>6642663651</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8835,64 +8831,56 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>13-08-1981</t>
+          <t>06-07-1999</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>ANGYECB81@GMAIL.COM</t>
+          <t>NAOMI.MORAILA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>17-02-2026 18:35:35</t>
+          <t>08-02-2026 09:55:33</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>17-02-2026 18:41:17</t>
+          <t>08-02-2026 10:00:42</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>17-02-2026 18:40:43</t>
-        </is>
-      </c>
+          <t>08-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8900,36 +8888,40 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26070522442290003600</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr"/>
+          <t>26070522169030002877</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>342079</t>
+          <t>341903</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19897</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8939,99 +8931,95 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>JESSICA</t>
+          <t>EDGAR OSVALDO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ANGUIANO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6647745824</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>30-04-2010</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>OFALOFALIN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>08-02-2026 10:47:34</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>08-02-2026 10:49:56</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>08-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>08-02-2026 10:49:29</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>6198452946</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VISTA RIO </t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>24-11-1993</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>AURI.SOTO7373@ICLOUD.COM</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>09-02-2026 09:49:03</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>No Forzoso</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>RECURRENTE $649 LE</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>19-02-2026 09:05:51</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>19-02-2026 09:04:38</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9039,27 +9027,19 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26070522489830003736</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>TOMAS HERNANDEZ MARTINEZ</t>
-        </is>
-      </c>
+          <t>26070522170000002882</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9071,12 +9051,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>342990</t>
+          <t>344666</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20807</t>
+          <t>22483</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9086,17 +9066,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RICARDO EMANUEL</t>
+          <t>MARIA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CARBO</t>
+          <t xml:space="preserve">CARDENAS </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>BUENROSTRO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9106,67 +9086,79 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6634418989</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>6641235751</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>JARDINES</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>19-10-2008</t>
+          <t>13-08-1981</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CARBORICARDO54@GMAIL.COM</t>
+          <t>ANGYECB81@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>11-02-2026 14:42:11</t>
+          <t>17-02-2026 18:35:35</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>11-02-2026 14:43:20</t>
+          <t>17-02-2026 18:41:17</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>17-02-2026 18:40:43</t>
+        </is>
+      </c>
       <c r="U65" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9174,14 +9166,14 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26070522265400003178</t>
+          <t>26070522442290003600</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
@@ -9198,12 +9190,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>342421</t>
+          <t>342079</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20239</t>
+          <t>19897</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9213,30 +9205,34 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIA </t>
+          <t>JESSICA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KATELYNN</t>
+          <t>ANGUIANO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6199042648</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>6198452946</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VISTA RIO </t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9244,17 +9240,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>24-11-2006</t>
+          <t>24-11-1993</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>LIAKATELYNN@GMAIL.COM</t>
+          <t>AURI.SOTO7373@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>09-02-2026 19:03:50</t>
+          <t>09-02-2026 09:49:03</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9264,36 +9260,44 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>09-02-2026 19:04:40</t>
+          <t>19-02-2026 09:05:51</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>19-02-2026 09:04:38</t>
+        </is>
+      </c>
       <c r="U66" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9301,19 +9305,27 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26070522209400002997</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
+          <t>26070522489830003736</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -9325,12 +9337,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>342473</t>
+          <t>342990</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>20807</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9340,17 +9352,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NANCY ADJANI</t>
+          <t>RICARDO EMANUEL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CARMONA</t>
+          <t>CARBO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9360,75 +9372,67 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6645921764</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
+          <t>6634418989</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>03-05-2004</t>
+          <t>19-10-2008</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>ADJANIAVILA123@GMAIL.COM</t>
+          <t>CARBORICARDO54@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>09-02-2026 20:02:24</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>11-02-2026 14:42:11</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>09-02-2026 20:06:57</t>
+          <t>11-02-2026 14:43:20</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>09-02-2026 20:05:35</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9436,36 +9440,36 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26070522212990003013</t>
+          <t>26070522265400003178</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>342991</t>
+          <t>342421</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20808</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9475,17 +9479,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>PEDRO RENE</t>
+          <t xml:space="preserve">LIA </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">PADILLA </t>
+          <t>KATELYNN</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>GERALDO</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9495,28 +9499,28 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6641174262</t>
+          <t>6199042648</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>20-07-2008</t>
+          <t>24-11-2006</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>PEDRO.PADILLA.GERALDO@GMAIL.COM</t>
+          <t>LIAKATELYNN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>11-02-2026 14:44:37</t>
+          <t>09-02-2026 19:03:50</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -9541,12 +9545,12 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>11-02-2026 14:45:21</t>
+          <t>09-02-2026 19:04:40</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -9563,7 +9567,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26070522265440003179</t>
+          <t>26070522209400002997</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
@@ -9575,24 +9579,24 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>342675</t>
+          <t>342473</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>20290</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9602,17 +9606,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EDGAR OMAR</t>
+          <t>NANCY ADJANI</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CARMONA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MEJIA</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9622,32 +9626,32 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6647499507</t>
+          <t>6645921764</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>31-01-1991</t>
+          <t>03-05-2004</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>RODRIGUEZEDGAR181@GMAIL.COM</t>
+          <t>ADJANIAVILA123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>10-02-2026 15:36:59</t>
+          <t>09-02-2026 20:02:24</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9668,17 +9672,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>10-02-2026 15:39:40</t>
+          <t>09-02-2026 20:06:57</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>10-02-2026 15:39:00</t>
+          <t>09-02-2026 20:05:35</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -9688,7 +9692,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -9698,7 +9702,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26070522235030003086</t>
+          <t>26070522212990003013</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr"/>
@@ -9710,24 +9714,24 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>343711</t>
+          <t>342675</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>21528</t>
+          <t>20492</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9737,32 +9741,32 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>JOSÉ</t>
+          <t>EDGAR OMAR</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MEJIA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>5303518187</t>
+          <t>6647499507</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>REFC</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9772,24 +9776,20 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>22-09-1990</t>
+          <t>31-01-1991</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>JSANCHEZ2930@YAHOO.COM</t>
+          <t>RODRIGUEZEDGAR181@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>14-02-2026 11:34:46</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 15:36:59</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9807,17 +9807,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>16-02-2026 22:40:49</t>
+          <t>10-02-2026 15:39:40</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>16-02-2026 22:40:21</t>
+          <t>10-02-2026 15:39:00</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -9837,14 +9837,10 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26070522411930003534</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26070522235030003086</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
@@ -9865,12 +9861,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>343867</t>
+          <t>342991</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21684</t>
+          <t>20808</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9880,17 +9876,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ANGEL ALBERTO</t>
+          <t>PEDRO RENE</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t xml:space="preserve">PADILLA </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>GERALDO</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9900,7 +9896,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6648158884</t>
+          <t>6641174262</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9911,17 +9907,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>11-10-2009</t>
+          <t>20-07-2008</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>AMORALES1124@BC.CONALEP.EDU.MX</t>
+          <t>PEDRO.PADILLA.GERALDO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>15-02-2026 14:12:34</t>
+          <t>11-02-2026 14:44:37</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9946,12 +9942,12 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>15-02-2026 14:13:28</t>
+          <t>11-02-2026 14:45:21</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -9968,7 +9964,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26070522367250003437</t>
+          <t>26070522265440003179</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
@@ -9980,12 +9976,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -10127,12 +10123,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>344168</t>
+          <t>343711</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21985</t>
+          <t>21528</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10142,30 +10138,34 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ISMAEL</t>
+          <t>JOSÉ</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OLIVAREZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>OROZCO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6631548170</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>5303518187</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>REFC</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -10173,42 +10173,42 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>15-03-1991</t>
+          <t>22-09-1990</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>ISMAELOLI9115@GMAIL.COM</t>
+          <t>JSANCHEZ2930@YAHOO.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>16-02-2026 16:33:44</t>
+          <t>14-02-2026 11:34:46</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>16-02-2026 16:34:44</t>
+          <t>16-02-2026 22:40:49</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -10216,13 +10216,21 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr"/>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>16-02-2026 22:40:21</t>
+        </is>
+      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W73" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10230,14 +10238,18 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26070522395910003498</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr"/>
+          <t>26070522411930003534</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
@@ -10254,12 +10266,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>344933</t>
+          <t>343867</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>22750</t>
+          <t>21684</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10269,17 +10281,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CLAUDIA CECILIA</t>
+          <t>ANGEL ALBERTO</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>DUEÑAS</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10289,79 +10301,67 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6643276502</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>YT</t>
-        </is>
-      </c>
+          <t>6648158884</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>03-02-1979</t>
+          <t>11-10-2009</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CDUENAS@TE.COM</t>
+          <t>AMORALES1124@BC.CONALEP.EDU.MX</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>18-02-2026 18:55:07</t>
+          <t>15-02-2026 14:12:34</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>18-02-2026 18:57:47</t>
+          <t>15-02-2026 14:13:28</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>18-02-2026 18:57:20</t>
-        </is>
-      </c>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10369,36 +10369,36 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26070522473870003705</t>
+          <t>26070522367250003437</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>345113</t>
+          <t>345876</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>87278</t>
+          <t>88041</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE FRANCISCO </t>
+          <t>YANELY IZAMAR</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SALDAÑA</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>ZACARIAS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -10428,28 +10428,28 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6631278884</t>
+          <t>6645810733</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>24-01-1996</t>
+          <t>29-11-1994</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>JOSESALDANA1996@ICLOUD.COM</t>
+          <t>ZACARIASYANELY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>19-02-2026 15:57:19</t>
+          <t>23-02-2026 16:35:07</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -10464,28 +10464,28 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>19-02-2026 15:58:10</t>
+          <t>23-02-2026 16:36:42</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V75" t="inlineStr"/>
@@ -10496,14 +10496,14 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26070522497920003762</t>
+          <t>26070522587680003928</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
@@ -10520,12 +10520,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>344306</t>
+          <t>346009</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>22123</t>
+          <t>88174</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10535,17 +10535,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SYLVANNA</t>
+          <t>CESAR JESUS</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LOYA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10555,28 +10555,32 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6642635718</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>6442591138</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>21-08-2014</t>
+          <t>29-08-1995</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>SYLVANNALOYACRUZ@GMAIL.COM</t>
+          <t>CESARJ3480@GMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>16-02-2026 18:40:11</t>
+          <t>23-02-2026 18:57:52</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -10586,36 +10590,44 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>18-02-2026 16:43:12</t>
+          <t>23-02-2026 19:04:04</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:03:20</t>
+        </is>
+      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr"/>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W76" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10623,18 +10635,14 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26070522467040003667</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26070522598280003955</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
@@ -10651,12 +10659,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>345119</t>
+          <t>344168</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>87284</t>
+          <t>21985</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10666,17 +10674,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEBASTIAN </t>
+          <t>ISMAEL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALVAREZ </t>
+          <t>OLIVAREZ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>OROZCO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10686,7 +10694,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6643203595</t>
+          <t>6631548170</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10697,17 +10705,17 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>30-09-1999</t>
+          <t>15-03-1991</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>ALVAREZX19221@GMAIL.COM</t>
+          <t>ISMAELOLI9115@GMAIL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>19-02-2026 16:07:14</t>
+          <t>16-02-2026 16:33:44</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -10722,22 +10730,22 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>19-02-2026 16:08:35</t>
+          <t>16-02-2026 16:34:44</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
@@ -10754,22 +10762,546 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26070522498190003763</t>
+          <t>26070522395910003498</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>344306</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>22123</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SYLVANNA</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>LOYA</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>6642635718</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>21-08-2014</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>SYLVANNALOYACRUZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>16-02-2026 18:40:11</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>18-02-2026 16:43:12</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>26070522467040003667</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>344933</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>22750</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>CLAUDIA CECILIA</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>DUEÑAS</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>6643276502</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>YT</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>03-02-1979</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>CDUENAS@TE.COM</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:55:07</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:57:47</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:57:20</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>26070522473870003705</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>345119</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>87284</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEBASTIAN </t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALVAREZ </t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>DUARTE</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>6643203595</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>30-09-1999</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>ALVAREZX19221@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>19-02-2026 16:07:14</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>19-02-2026 16:08:35</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>26070522498190003763</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>345113</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>87278</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE FRANCISCO </t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>SALDAÑA</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>6631278884</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>24-01-1996</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>JOSESALDANA1996@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>19-02-2026 15:57:19</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>19-02-2026 15:58:10</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>26070522497920003762</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PAPALOTE TJ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PAPALOTE TJ.xlsx
@@ -1257,12 +1257,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>320062</t>
+          <t>316042</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17559</t>
+          <t>13541</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROCIO CAROLINA </t>
+          <t xml:space="preserve">SOFIA ITZEL </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>WONG</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>BARBOZA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6643764420</t>
+          <t>6631678655</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>C ANTARES 600 A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1307,24 +1307,20 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>15-08-1983</t>
+          <t>05-08-2009</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CHERRERA090913@GMAIL.COM</t>
+          <t>ITZELSWP@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22-10-2025 17:16:08</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>27-09-2025 11:49:10</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1342,17 +1338,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>20-02-2026 18:23:39</t>
+          <t>02-02-2026 09:02:57</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>20-02-2026 18:22:55</t>
+          <t>02-02-2026 09:02:11</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1372,19 +1368,15 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26070522534060003843</t>
+          <t>26070522002130002338</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>TOMAS HERNANDEZ MARTINEZ</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
           <t>499</t>
@@ -1392,7 +1384,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1404,12 +1396,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>316042</t>
+          <t>320062</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>17559</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1419,17 +1411,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOFIA ITZEL </t>
+          <t xml:space="preserve">ROCIO CAROLINA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WONG</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BARBOZA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1439,12 +1431,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6631678655</t>
+          <t>6643764420</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C ANTARES 600 A</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1454,20 +1446,24 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>05-08-2009</t>
+          <t>15-08-1983</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ITZELSWP@GMAIL.COM</t>
+          <t>CHERRERA090913@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>27-09-2025 11:49:10</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>22-10-2025 17:16:08</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1485,17 +1481,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-02-2026 09:02:57</t>
+          <t>20-02-2026 18:23:39</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-02-2026 09:02:11</t>
+          <t>20-02-2026 18:22:55</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1515,15 +1511,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26070522002130002338</t>
+          <t>26070522534060003843</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>499</t>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -2508,12 +2508,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>339879</t>
+          <t>341393</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17697</t>
+          <t>19211</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2523,17 +2523,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ANGELICA MARIA</t>
+          <t>JOLETTE MAYRELI</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>CARDONA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HIGUERA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2543,14 +2543,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6641203191</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>LAGO TEQUESQUITENGO 5205-A</t>
-        </is>
-      </c>
+          <t>6647097237</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2558,17 +2554,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>21-11-1965</t>
+          <t>07-11-2005</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ANGYEBEBA1965@HOTMAIL.COM</t>
+          <t>JOLETTECARDONA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-02-2026 07:27:15</t>
+          <t>05-02-2026 17:12:47</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2578,44 +2574,36 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-02-2026 07:33:19</t>
+          <t>05-02-2026 17:13:47</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>02-02-2026 07:31:50</t>
-        </is>
-      </c>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2623,19 +2611,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26070521999640002330</t>
+          <t>26070522112250002720</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2647,12 +2635,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>341393</t>
+          <t>339879</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19211</t>
+          <t>17697</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2662,17 +2650,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JOLETTE MAYRELI</t>
+          <t>ANGELICA MARIA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CARDONA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>HIGUERA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2682,10 +2670,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6647097237</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6641203191</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LAGO TEQUESQUITENGO 5205-A</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2693,17 +2685,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>07-11-2005</t>
+          <t>21-11-1965</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>JOLETTECARDONA@GMAIL.COM</t>
+          <t>ANGYEBEBA1965@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>05-02-2026 17:12:47</t>
+          <t>02-02-2026 07:27:15</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2713,36 +2705,44 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>05-02-2026 17:13:47</t>
+          <t>02-02-2026 07:33:19</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>02-02-2026 07:31:50</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2750,19 +2750,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26070522112250002720</t>
+          <t>26070521999640002330</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>340283</t>
+          <t>341892</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18101</t>
+          <t>19710</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2924,17 +2924,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ALONDRA</t>
+          <t>JUANA MARIA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>LANDEROS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6647699094</t>
+          <t>6647297856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2955,17 +2955,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>16-05-2009</t>
+          <t>12-07-1978</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ALONDRACASTRODOMINGUEZ@GMAIL.COM</t>
+          <t>PENDIENTE.JUANA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-02-2026 16:43:22</t>
+          <t>08-02-2026 10:02:26</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2990,18 +2990,18 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-02-2026 16:44:42</t>
+          <t>08-02-2026 10:04:29</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26070522017160002390</t>
+          <t>26070522169130002878</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Jesus Alejandro  Partida Partida</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3036,12 +3036,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341892</t>
+          <t>340283</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>18101</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3051,17 +3051,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JUANA MARIA</t>
+          <t>ALONDRA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LANDEROS</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6647297856</t>
+          <t>6647699094</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3082,17 +3082,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>12-07-1978</t>
+          <t>16-05-2009</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PENDIENTE.JUANA@GMAIL.COM</t>
+          <t>ALONDRACASTRODOMINGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>08-02-2026 10:02:26</t>
+          <t>02-02-2026 16:43:22</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3117,18 +3117,18 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>08-02-2026 10:04:29</t>
+          <t>02-02-2026 16:44:42</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26070522169130002878</t>
+          <t>26070522017160002390</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Jesus Alejandro  Partida Partida</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3965,12 +3965,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>340004</t>
+          <t>340179</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17822</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3980,17 +3980,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EZEQUIEL</t>
+          <t>JUAN ANTONIO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GASTELUM</t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MÉNDEZ</t>
+          <t>URIARTE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4000,10 +4000,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6645318296</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>6291079920</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>JFHF</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4011,42 +4015,38 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>02-07-2007</t>
+          <t>18-01-2007</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>EZEQUIELGASTELUM2@GMAIL.COM</t>
+          <t>JUANMURILLOU@EDUBC.COM.MX</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-02-2026 10:18:49</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 14:35:17</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-02-2026 10:26:32</t>
+          <t>02-02-2026 14:38:10</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4054,13 +4054,21 @@
           <t>02-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>02-02-2026 14:37:37</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4068,19 +4076,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26070522004870002347</t>
+          <t>26070522013130002376</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4092,12 +4100,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>341175</t>
+          <t>340004</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18993</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4107,17 +4115,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>BRIANA TERESA</t>
+          <t>EZEQUIEL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEA </t>
+          <t>GASTELUM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MÉNDEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4127,75 +4135,67 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6645681580</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>REF</t>
-        </is>
-      </c>
+          <t>6645318296</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>29-10-2011</t>
+          <t>02-07-2007</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>BRIANA.VEAS@ICLOUD.COM</t>
+          <t>EZEQUIELGASTELUM2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>04-02-2026 19:34:05</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>02-02-2026 10:18:49</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>04-02-2026 19:36:22</t>
+          <t>02-02-2026 10:26:32</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>04-02-2026 19:35:54</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4203,19 +4203,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26070522088290002649</t>
+          <t>26070522004870002347</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4227,12 +4227,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>340179</t>
+          <t>341175</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>18993</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4242,17 +4242,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JUAN ANTONIO</t>
+          <t>BRIANA TERESA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t xml:space="preserve">VEA </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>URIARTE</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4262,32 +4262,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6291079920</t>
+          <t>6645681580</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>JFHF</t>
+          <t>REF</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>18-01-2007</t>
+          <t>29-10-2011</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>JUANMURILLOU@EDUBC.COM.MX</t>
+          <t>BRIANA.VEAS@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>02-02-2026 14:35:17</t>
+          <t>04-02-2026 19:34:05</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4308,17 +4308,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>02-02-2026 14:38:10</t>
+          <t>04-02-2026 19:36:22</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>02-02-2026 14:37:37</t>
+          <t>04-02-2026 19:35:54</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26070522013130002376</t>
+          <t>26070522088290002649</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4489,12 +4489,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>340699</t>
+          <t>340704</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4504,17 +4504,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NOE ALEJANDRO</t>
+          <t>ALMA JUDITH</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>MARTÍNEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4524,10 +4524,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6631565587</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>6631064684</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4535,56 +4539,60 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>13-09-2001</t>
+          <t>08-12-1987</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>TNAMELESS9@GMAIL.COM</t>
+          <t>ALMITA2015.ABE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>03-02-2026 17:04:19</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 17:09:20</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>03-02-2026 17:06:08</t>
+          <t>10-02-2026 17:21:55</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>10-02-2026 17:21:14</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4592,14 +4600,18 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26070522047920002489</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr"/>
+          <t>26070522239480003099</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4616,12 +4628,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>340176</t>
+          <t>340810</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17994</t>
+          <t>18628</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4631,17 +4643,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LEOBARDO</t>
+          <t>DANIA GISSEL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4651,32 +4663,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6652803978</t>
+          <t>6632070260</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>YUY</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18-10-1970</t>
+          <t>16-09-1997</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>LGARCIAJ@EDUBC.COM.MX</t>
+          <t>TDNDANIAMENA0321@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>02-02-2026 14:31:22</t>
+          <t>03-02-2026 19:17:52</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4697,17 +4709,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>02-02-2026 14:34:05</t>
+          <t>03-02-2026 19:19:54</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>02-02-2026 14:33:25</t>
+          <t>03-02-2026 19:19:41</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4727,7 +4739,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26070522013020002374</t>
+          <t>26070522055720002525</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4739,7 +4751,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4751,12 +4763,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>340704</t>
+          <t>340863</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18522</t>
+          <t>18681</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4766,17 +4778,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ALMA JUDITH</t>
+          <t>ANGIE PAOLA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MARTÍNEZ</t>
+          <t>PELAEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4786,12 +4798,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6631064684</t>
+          <t>7441284622</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>COL LA LAJA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4801,48 +4813,52 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>08-12-1987</t>
+          <t>03-06-1997</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ALMITA2015.ABE@GMAIL.COM</t>
+          <t>ANGIE.PLZ@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>03-02-2026 17:09:20</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>04-02-2026 06:23:44</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10-02-2026 17:21:55</t>
+          <t>05-02-2026 06:25:32</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>10-02-2026 17:21:14</t>
+          <t>05-02-2026 06:23:59</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4852,7 +4868,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4862,23 +4878,27 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26070522239480003099</t>
+          <t>26070522098680002660</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4890,12 +4910,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>340810</t>
+          <t>340176</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>17994</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4905,17 +4925,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DANIA GISSEL</t>
+          <t>LEOBARDO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4925,32 +4945,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6632070260</t>
+          <t>6652803978</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>YUY</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>16-09-1997</t>
+          <t>18-10-1970</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>TDNDANIAMENA0321@GMAIL.COM</t>
+          <t>LGARCIAJ@EDUBC.COM.MX</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>03-02-2026 19:17:52</t>
+          <t>02-02-2026 14:31:22</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4971,17 +4991,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>03-02-2026 19:19:54</t>
+          <t>02-02-2026 14:34:05</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>03-02-2026 19:19:41</t>
+          <t>02-02-2026 14:33:25</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5001,7 +5021,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26070522055720002525</t>
+          <t>26070522013020002374</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -5013,7 +5033,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5025,12 +5045,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>340863</t>
+          <t>340699</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18681</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5040,17 +5060,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ANGIE PAOLA</t>
+          <t>NOE ALEJANDRO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>NAVARRETE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PELAEZ</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5060,14 +5080,10 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7441284622</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>COL LA LAJA</t>
-        </is>
-      </c>
+          <t>6631565587</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5075,17 +5091,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>03-06-1997</t>
+          <t>13-09-2001</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>ANGIE.PLZ@OUTLOOK.COM</t>
+          <t>TNAMELESS9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>04-02-2026 06:23:44</t>
+          <t>03-02-2026 17:04:19</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5095,44 +5111,36 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>05-02-2026 06:25:32</t>
+          <t>03-02-2026 17:06:08</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>05-02-2026 06:23:59</t>
-        </is>
-      </c>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5140,27 +5148,19 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26070522098680002660</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>TOMAS HERNANDEZ MARTINEZ</t>
-        </is>
-      </c>
+          <t>26070522047920002489</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5172,12 +5172,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>340910</t>
+          <t>340321</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ANA</t>
+          <t xml:space="preserve">PRISELLA JACQUELINE </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t xml:space="preserve">ARELLANO </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6195302607</t>
+          <t>6196224376</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AV DE CHAPALA 4635 COL EL LAGO</t>
+          <t>EL PEDREGAL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5222,17 +5222,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>09-06-1995</t>
+          <t>17-07-1997</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ANAELSACARBAJAL84@GMAIL.COM</t>
+          <t>PRISELLAARELLANO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>04-02-2026 09:22:30</t>
+          <t>02-02-2026 17:53:14</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5253,17 +5253,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>09-02-2026 09:58:45</t>
+          <t>03-02-2026 12:33:38</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>09-02-2026 09:57:56</t>
+          <t>03-02-2026 12:32:24</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5283,19 +5283,11 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26070522187140002917</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>TOMAS HERNANDEZ MARTINEZ</t>
-        </is>
-      </c>
+          <t>26070522038540002452</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
           <t>499</t>
@@ -5303,7 +5295,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Jesus Alejandro  Partida Partida</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5315,12 +5307,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>340321</t>
+          <t>341172</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18139</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5330,17 +5322,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRISELLA JACQUELINE </t>
+          <t xml:space="preserve">YAMIL EDEN </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARELLANO </t>
+          <t>AVITIA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5350,32 +5342,32 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6196224376</t>
+          <t>6632013605</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>EL PEDREGAL</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>17-07-1997</t>
+          <t>19-09-2006</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>PRISELLAARELLANO@GMAIL.COM</t>
+          <t>YAMILAVITIA61@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>02-02-2026 17:53:14</t>
+          <t>04-02-2026 19:27:23</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5386,7 +5378,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -5396,17 +5388,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>03-02-2026 12:33:38</t>
+          <t>04-02-2026 19:32:29</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>03-02-2026 12:32:24</t>
+          <t>04-02-2026 19:32:02</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5416,7 +5408,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5426,7 +5418,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26070522038540002452</t>
+          <t>26070522088210002648</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5438,7 +5430,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5450,12 +5442,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342214</t>
+          <t>341225</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>19043</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5465,17 +5457,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR EDUARDO </t>
+          <t>BLANCA EDITH</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>DOMÍNGUEZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MONDRAGÓN</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5485,32 +5477,32 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6641272476</t>
+          <t>6644725233</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DAS</t>
+          <t>BALKASH</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>07-11-2005</t>
+          <t>02-02-2002</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>EL7615132@GMAIL.COM</t>
+          <t>MONDRAGONBLANCA87@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>09-02-2026 15:32:17</t>
+          <t>05-02-2026 07:42:04</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5521,7 +5513,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -5531,17 +5523,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>09-02-2026 15:34:55</t>
+          <t>08-02-2026 10:45:59</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>09-02-2026 15:34:41</t>
+          <t>08-02-2026 10:43:52</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5561,7 +5553,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26070522195720002961</t>
+          <t>26070522169910002880</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5573,7 +5565,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5585,12 +5577,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>340534</t>
+          <t>340910</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5600,17 +5592,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BENIR ITZEL</t>
+          <t>ANA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NEVAREZ</t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5620,12 +5612,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6197169503</t>
+          <t>6195302607</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>C RIO BLANCO 394</t>
+          <t>AV DE CHAPALA 4635 COL EL LAGO</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5635,17 +5627,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>17-07-2004</t>
+          <t>09-06-1995</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ITZELNEVARZ@GMAIL.COM</t>
+          <t>ANAELSACARBAJAL84@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>03-02-2026 12:00:41</t>
+          <t>04-02-2026 09:22:30</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5666,17 +5658,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>05-02-2026 12:21:39</t>
+          <t>09-02-2026 09:58:45</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>05-02-2026 12:21:14</t>
+          <t>09-02-2026 09:57:56</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5686,7 +5678,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5696,7 +5688,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26070522104310002678</t>
+          <t>26070522187140002917</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5704,7 +5696,11 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>499</t>
@@ -5712,7 +5708,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Jesus Alejandro  Partida Partida</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5724,12 +5720,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>340696</t>
+          <t>340534</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18514</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5739,30 +5735,34 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ANA JOSELYN</t>
+          <t>BENIR ITZEL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ARIPEZ</t>
+          <t>NEVAREZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6643624758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>6197169503</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>C RIO BLANCO 394</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5770,56 +5770,60 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>09-04-2001</t>
+          <t>17-07-2004</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ANNAVAZQUEZ04@GMAIL.COM</t>
+          <t>ITZELNEVARZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>03-02-2026 17:01:07</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 12:00:41</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>03-02-2026 17:02:58</t>
+          <t>05-02-2026 12:21:39</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>05-02-2026 12:21:14</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5827,19 +5831,23 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26070522047750002488</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
+          <t>26070522104310002678</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5851,12 +5859,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>340893</t>
+          <t>342214</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18711</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5866,17 +5874,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>PRISILA</t>
+          <t xml:space="preserve">VICTOR EDUARDO </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5886,32 +5894,32 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6645204741</t>
+          <t>6641272476</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PRIV TEQUESQUITENGO 204</t>
+          <t>DAS</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>05-02-1997</t>
+          <t>07-11-2005</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>KITTYPEACE1@HOTMAIL.COM</t>
+          <t>EL7615132@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>04-02-2026 08:27:45</t>
+          <t>09-02-2026 15:32:17</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5932,17 +5940,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>04-02-2026 08:37:12</t>
+          <t>09-02-2026 15:34:55</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>04-02-2026 08:32:48</t>
+          <t>09-02-2026 15:34:41</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5952,7 +5960,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5962,7 +5970,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26070522069700002552</t>
+          <t>26070522195720002961</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -5974,7 +5982,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5986,12 +5994,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>341172</t>
+          <t>340696</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6001,17 +6009,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">YAMIL EDEN </t>
+          <t>ANA JOSELYN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AVITIA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ARIPEZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6021,75 +6029,67 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6632013605</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
+          <t>6643624758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>19-09-2006</t>
+          <t>09-04-2001</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>YAMILAVITIA61@GMAIL.COM</t>
+          <t>ANNAVAZQUEZ04@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>04-02-2026 19:27:23</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>03-02-2026 17:01:07</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>04-02-2026 19:32:29</t>
+          <t>03-02-2026 17:02:58</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>04-02-2026 19:32:02</t>
-        </is>
-      </c>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6097,14 +6097,14 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26070522088210002648</t>
+          <t>26070522047750002488</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6121,12 +6121,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>341225</t>
+          <t>340893</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19043</t>
+          <t>18711</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6136,17 +6136,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BLANCA EDITH</t>
+          <t>PRISILA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>DOMÍNGUEZ</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MONDRAGÓN</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6644725233</t>
+          <t>6645204741</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>BALKASH</t>
+          <t>PRIV TEQUESQUITENGO 204</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6171,17 +6171,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>02-02-2002</t>
+          <t>05-02-1997</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>MONDRAGONBLANCA87@GMAIL.COM</t>
+          <t>KITTYPEACE1@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>05-02-2026 07:42:04</t>
+          <t>04-02-2026 08:27:45</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -6202,17 +6202,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>08-02-2026 10:45:59</t>
+          <t>04-02-2026 08:37:12</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>08-02-2026 10:43:52</t>
+          <t>04-02-2026 08:32:48</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26070522169910002880</t>
+          <t>26070522069700002552</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6780,12 +6780,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>341234</t>
+          <t>341842</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19052</t>
+          <t>19660</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CLAUDIA JANETH</t>
+          <t xml:space="preserve">MARIA SULEMA </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ONTIVEROS</t>
+          <t>CUAMATZI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GALINDO</t>
+          <t xml:space="preserve">PUERTO </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6645527209</t>
+          <t>6645281374</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">C ADOLFO LOPEZMATEOS 6413 </t>
+          <t>SD</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>27-02-1995</t>
+          <t>19-05-2005</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLAUDIADSLINDUSTRIAL@OUTLOOK.COM</t>
+          <t>CUAMATZIMARIA1720@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>05-02-2026 08:15:20</t>
+          <t>07-02-2026 14:33:00</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6861,17 +6861,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>11-02-2026 08:26:30</t>
+          <t>07-02-2026 14:38:14</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>11-02-2026 08:26:00</t>
+          <t>07-02-2026 14:37:48</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6891,14 +6891,10 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26070522259580003154</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26070522162170002874</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6907,7 +6903,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Jesus Alejandro  Partida Partida</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6919,12 +6915,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>341903</t>
+          <t>341905</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19721</t>
+          <t>19723</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6934,7 +6930,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EDGAR OSVALDO</t>
+          <t xml:space="preserve">ALIZON </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6954,32 +6950,32 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6647745824</t>
+          <t>6632243995</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>30-04-2010</t>
+          <t>14-05-2009</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>OFALOFALIN@GMAIL.COM</t>
+          <t>WAYTOJUNI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>08-02-2026 10:47:34</t>
+          <t>08-02-2026 10:51:13</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6990,7 +6986,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -7000,7 +6996,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>08-02-2026 10:49:56</t>
+          <t>08-02-2026 10:53:01</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -7010,7 +7006,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>08-02-2026 10:49:29</t>
+          <t>08-02-2026 10:52:34</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7030,7 +7026,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26070522170000002882</t>
+          <t>26070522170030002883</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -7054,12 +7050,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>344438</t>
+          <t>342057</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22255</t>
+          <t>19875</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7069,17 +7065,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ALEXIS</t>
+          <t>FRANCISCO ROSARIO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>VELA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7089,12 +7085,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6634626985</t>
+          <t>6871795893</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>C DIAMANTE 109 5</t>
+          <t>PORTOFINO 2028 A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7104,52 +7100,52 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>16-08-2000</t>
+          <t>03-02-1998</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ALEXIS.LOPEZZ1608@GMAIL.COM</t>
+          <t>FRANCISCOHDZ.0298@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>17-02-2026 10:10:27</t>
+          <t>09-02-2026 08:52:27</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>17-02-2026 10:19:08</t>
+          <t>13-02-2026 07:07:01</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>17-02-2026 10:16:01</t>
+          <t>13-02-2026 07:03:42</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7169,14 +7165,18 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26070522423830003542</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr"/>
+          <t>26070522315080003331</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -7193,12 +7193,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>345666</t>
+          <t>342077</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>87831</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CAROLINA</t>
+          <t>MONICA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ARMENTA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7228,14 +7228,10 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6645204568</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>C PUERTO ESCONDIDO 20139</t>
-        </is>
-      </c>
+          <t>6643727163</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7243,64 +7239,56 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>02-04-1991</t>
+          <t>23-09-1993</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>KAR0LINA89@HOTMAIL.COM</t>
+          <t>MONICA.GTZ939@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>23-02-2026 08:05:33</t>
+          <t>09-02-2026 09:46:37</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>23-02-2026 08:12:41</t>
+          <t>19-02-2026 09:07:04</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>23-02-2026 08:11:48</t>
-        </is>
-      </c>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7308,14 +7296,18 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26070522573540003894</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr"/>
+          <t>26070522489860003737</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7332,12 +7324,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>341842</t>
+          <t>344438</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19660</t>
+          <t>22255</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7347,17 +7339,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA SULEMA </t>
+          <t>ALEXIS</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CUAMATZI</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">PUERTO </t>
+          <t>VELA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7367,35 +7359,39 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6645281374</t>
+          <t>6634626985</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>C DIAMANTE 109 5</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>19-05-2005</t>
+          <t>16-08-2000</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CUAMATZIMARIA1720@GMAIL.COM</t>
+          <t>ALEXIS.LOPEZZ1608@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>07-02-2026 14:33:00</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>17-02-2026 10:10:27</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7413,17 +7409,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>07-02-2026 14:38:14</t>
+          <t>17-02-2026 10:19:08</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>07-02-2026 14:37:48</t>
+          <t>17-02-2026 10:16:01</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7443,7 +7439,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26070522162170002874</t>
+          <t>26070522423830003542</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7467,12 +7463,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>341905</t>
+          <t>345666</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19723</t>
+          <t>87831</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7482,17 +7478,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALIZON </t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>ARMENTA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7502,12 +7498,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6632243995</t>
+          <t>6645204568</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>C PUERTO ESCONDIDO 20139</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7517,20 +7513,24 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>14-05-2009</t>
+          <t>02-04-1991</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>WAYTOJUNI@GMAIL.COM</t>
+          <t>KAR0LINA89@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>08-02-2026 10:51:13</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>23-02-2026 08:05:33</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7548,17 +7548,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>08-02-2026 10:53:01</t>
+          <t>23-02-2026 08:12:41</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>08-02-2026 10:52:34</t>
+          <t>23-02-2026 08:11:48</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26070522170030002883</t>
+          <t>26070522573540003894</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7602,12 +7602,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>342057</t>
+          <t>341234</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>19052</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7617,17 +7617,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FRANCISCO ROSARIO</t>
+          <t>CLAUDIA JANETH</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>ONTIVEROS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GALINDO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7637,67 +7637,63 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6871795893</t>
+          <t>6645527209</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>PORTOFINO 2028 A</t>
+          <t xml:space="preserve">C ADOLFO LOPEZMATEOS 6413 </t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>03-02-1998</t>
+          <t>27-02-1995</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>FRANCISCOHDZ.0298@GMAIL.COM</t>
+          <t>CLAUDIADSLINDUSTRIAL@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>09-02-2026 08:52:27</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 08:15:20</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>13-02-2026 07:07:01</t>
+          <t>11-02-2026 08:26:30</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>13-02-2026 07:03:42</t>
+          <t>11-02-2026 08:26:00</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7707,7 +7703,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7717,7 +7713,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26070522315080003331</t>
+          <t>26070522259580003154</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7728,12 +7724,12 @@
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Jesus Alejandro  Partida Partida</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7745,12 +7741,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>342077</t>
+          <t>341903</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7760,17 +7756,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MONICA</t>
+          <t>EDGAR OSVALDO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7780,67 +7776,75 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6643727163</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>6647745824</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>23-09-1993</t>
+          <t>30-04-2010</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>MONICA.GTZ939@GMAIL.COM</t>
+          <t>OFALOFALIN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>09-02-2026 09:46:37</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>08-02-2026 10:47:34</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>19-02-2026 09:07:04</t>
+          <t>08-02-2026 10:49:56</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr"/>
+          <t>08-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>08-02-2026 10:49:29</t>
+        </is>
+      </c>
       <c r="U55" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7848,23 +7852,19 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26070522489860003737</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26070522170000002882</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7876,12 +7876,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>341401</t>
+          <t>342166</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19219</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7891,17 +7891,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ALONDRA</t>
+          <t>MIA SHERLYN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>VELA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TREJO</t>
+          <t>ALEGRE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7911,14 +7911,10 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6647580850</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>C SONORA 4157</t>
-        </is>
-      </c>
+          <t>6647313220</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7926,60 +7922,56 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>02-01-1999</t>
+          <t>07-05-2008</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>AMTZT.02@GMAIL.COM</t>
+          <t>707MKSZK@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>05-02-2026 17:38:32</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>09-02-2026 13:48:38</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>07-02-2026 13:16:46</t>
+          <t>09-02-2026 13:49:41</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>07-02-2026 13:16:15</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7987,18 +7979,14 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26070522161600002868</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26070522192160002938</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -8015,12 +8003,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>342475</t>
+          <t>341401</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8030,17 +8018,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA JULIA </t>
+          <t>ALONDRA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>TREJO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8050,12 +8038,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6643714693</t>
+          <t>6647580850</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>C SONORA 4157</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -8065,17 +8053,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>07-12-1985</t>
+          <t>02-01-1999</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>AVILAJULIA746@GMAIL.COM</t>
+          <t>AMTZT.02@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>09-02-2026 20:08:38</t>
+          <t>05-02-2026 17:38:32</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -8096,17 +8084,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>09-02-2026 20:10:52</t>
+          <t>07-02-2026 13:16:46</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>09-02-2026 20:10:24</t>
+          <t>07-02-2026 13:16:15</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8116,7 +8104,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -8126,10 +8114,14 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26070522213060003014</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr"/>
+          <t>26070522161600002868</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
@@ -8138,7 +8130,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -8150,12 +8142,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>342166</t>
+          <t>342475</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8165,17 +8157,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MIA SHERLYN</t>
+          <t xml:space="preserve">ANA JULIA </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>VELA</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ALEGRE</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8185,10 +8177,14 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6647313220</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>6643714693</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8196,42 +8192,38 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>07-05-2008</t>
+          <t>07-12-1985</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>707MKSZK@GMAIL.COM</t>
+          <t>AVILAJULIA746@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>09-02-2026 13:48:38</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 20:08:38</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>09-02-2026 13:49:41</t>
+          <t>09-02-2026 20:10:52</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -8239,13 +8231,21 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr"/>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>09-02-2026 20:10:24</t>
+        </is>
+      </c>
       <c r="U58" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8253,19 +8253,19 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26070522192160002938</t>
+          <t>26070522213060003014</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -8277,12 +8277,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>341885</t>
+          <t>346339</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19703</t>
+          <t>88504</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8292,17 +8292,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAOMY JARALDY </t>
+          <t>JESUS EFREN</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MORAILA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8312,67 +8312,79 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6642663651</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>6645575982</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>06-07-1999</t>
+          <t>15-03-2000</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>NAOMI.MORAILA@GMAIL.COM</t>
+          <t>EFRENPEREZALVAREZ123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>08-02-2026 09:55:33</t>
+          <t>24-02-2026 21:17:00</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>08-02-2026 10:00:42</t>
+          <t>24-02-2026 21:21:18</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr"/>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>24-02-2026 21:20:31</t>
+        </is>
+      </c>
       <c r="U59" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8380,40 +8392,36 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26070522169030002877</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26070522637830004077</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>343380</t>
+          <t>341885</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21197</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8423,17 +8431,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>GRACIELA</t>
+          <t xml:space="preserve">NAOMY JARALDY </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>MORAILA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑA </t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8443,14 +8451,10 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6642061015</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>CALZ MEDITERRANEO</t>
-        </is>
-      </c>
+          <t>6642663651</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8458,60 +8462,56 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>02-10-1960</t>
+          <t>06-07-1999</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>GRACIELAHERNANDEZ26@GMAIL.COM</t>
+          <t>NAOMI.MORAILA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>12-02-2026 18:59:53</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>08-02-2026 09:55:33</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>12-02-2026 19:10:56</t>
+          <t>08-02-2026 10:00:42</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>12-02-2026 19:08:55</t>
-        </is>
-      </c>
+          <t>08-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8519,36 +8519,40 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26070522304190003308</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr"/>
+          <t>26070522169030002877</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>343488</t>
+          <t>342990</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21305</t>
+          <t>20807</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8558,17 +8562,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EILAN DUVIER ALFREDO</t>
+          <t>RICARDO EMANUEL</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>CARBO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PAREDES</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8578,14 +8582,10 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6645273986</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>C LAGO TOGO 5308 A 303</t>
-        </is>
-      </c>
+          <t>6634418989</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8593,60 +8593,56 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>25-11-2012</t>
+          <t>19-10-2008</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>DUVIER.701@ICLOUD.COM</t>
+          <t>CARBORICARDO54@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>13-02-2026 12:34:30</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>11-02-2026 14:42:11</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>13-02-2026 12:48:31</t>
+          <t>11-02-2026 14:43:20</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>13-02-2026 12:47:47</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8654,14 +8650,14 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26070522319940003345</t>
+          <t>26070522265400003178</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -8678,12 +8674,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>346339</t>
+          <t>342079</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>88504</t>
+          <t>19897</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8693,87 +8689,87 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>JESUS EFREN</t>
+          <t>JESSICA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>ANGUIANO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6645575982</t>
+          <t>6198452946</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t xml:space="preserve">VISTA RIO </t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>15-03-2000</t>
+          <t>24-11-1993</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>EFRENPEREZALVAREZ123@GMAIL.COM</t>
+          <t>AURI.SOTO7373@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>24-02-2026 21:17:00</t>
+          <t>09-02-2026 09:49:03</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>24-02-2026 21:21:18</t>
+          <t>19-02-2026 09:05:51</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>24-02-2026 21:20:31</t>
+          <t>19-02-2026 09:04:38</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8793,36 +8789,44 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26070522637830004077</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
+          <t>26070522489830003736</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>342079</t>
+          <t>343380</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>19897</t>
+          <t>21197</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8832,99 +8836,95 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>JESSICA</t>
+          <t>GRACIELA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ANGUIANO</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t xml:space="preserve">PEÑA </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6642061015</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>CALZ MEDITERRANEO</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>02-10-1960</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>GRACIELAHERNANDEZ26@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>12-02-2026 18:59:53</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>12-02-2026 19:10:56</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>12-02-2026 19:08:55</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>6198452946</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VISTA RIO </t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>24-11-1993</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>AURI.SOTO7373@ICLOUD.COM</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>09-02-2026 09:49:03</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>No Forzoso</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>RECURRENTE $649 LE</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>19-02-2026 09:05:51</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>19-02-2026 09:04:38</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="W63" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8932,44 +8932,36 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26070522489830003736</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>TOMAS HERNANDEZ MARTINEZ</t>
-        </is>
-      </c>
+          <t>26070522304190003308</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>343112</t>
+          <t>343488</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>21305</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8979,17 +8971,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NAYELY</t>
+          <t>EILAN DUVIER ALFREDO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PELAYO</t>
+          <t>PAREDES</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8999,67 +8991,75 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6865495658</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>6645273986</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>C LAGO TOGO 5308 A 303</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>13-05-1990</t>
+          <t>25-11-2012</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>NAYELY.JAUREGUI@GMAIL.COM</t>
+          <t>DUVIER.701@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>11-02-2026 19:01:35</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 12:34:30</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>18-02-2026 18:57:39</t>
+          <t>13-02-2026 12:48:31</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>13-02-2026 12:47:47</t>
+        </is>
+      </c>
       <c r="U64" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9067,36 +9067,36 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26070522473850003704</t>
+          <t>26070522319940003345</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>342990</t>
+          <t>346873</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20807</t>
+          <t>89038</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9106,17 +9106,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RICARDO EMANUEL</t>
+          <t>LUIS OSCAR</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CARBO</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9126,10 +9126,14 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6634418989</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>6645995563</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>C LOMA BONITA  17205 H</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9137,56 +9141,64 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>19-10-2008</t>
+          <t>16-07-1985</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CARBORICARDO54@GMAIL.COM</t>
+          <t>LONUFER09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>11-02-2026 14:42:11</t>
+          <t>27-02-2026 08:30:59</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>11-02-2026 14:43:20</t>
+          <t>27-02-2026 08:45:08</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr"/>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>27-02-2026 08:43:02</t>
+        </is>
+      </c>
       <c r="U65" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9194,36 +9206,36 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26070522265400003178</t>
+          <t>26070522706740004264</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>342421</t>
+          <t>343112</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20239</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9233,17 +9245,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIA </t>
+          <t>NAYELY</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KATELYNN</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>PELAYO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9253,7 +9265,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6199042648</t>
+          <t>6865495658</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9264,17 +9276,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>24-11-2006</t>
+          <t>13-05-1990</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>LIAKATELYNN@GMAIL.COM</t>
+          <t>NAYELY.JAUREGUI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>09-02-2026 19:03:50</t>
+          <t>11-02-2026 19:01:35</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9299,12 +9311,12 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>09-02-2026 19:04:40</t>
+          <t>18-02-2026 18:57:39</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -9321,7 +9333,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26070522209400002997</t>
+          <t>26070522473850003704</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
@@ -9333,24 +9345,24 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>342473</t>
+          <t>342421</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9360,17 +9372,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NANCY ADJANI</t>
+          <t xml:space="preserve">LIA </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CARMONA</t>
+          <t>KATELYNN</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9380,14 +9392,10 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6645921764</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
+          <t>6199042648</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9395,38 +9403,42 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>03-05-2004</t>
+          <t>24-11-2006</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>ADJANIAVILA123@GMAIL.COM</t>
+          <t>LIAKATELYNN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>09-02-2026 20:02:24</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>09-02-2026 19:03:50</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>09-02-2026 20:06:57</t>
+          <t>09-02-2026 19:04:40</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -9434,21 +9446,13 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>09-02-2026 20:05:35</t>
-        </is>
-      </c>
+      <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9456,19 +9460,19 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26070522212990003013</t>
+          <t>26070522209400002997</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -9480,12 +9484,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>344166</t>
+          <t>342473</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21983</t>
+          <t>20290</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9495,17 +9499,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BRENDA</t>
+          <t>NANCY ADJANI</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>CARMONA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9515,10 +9519,14 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6651072660</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>6645921764</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9526,56 +9534,60 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>22-06-1999</t>
+          <t>03-05-2004</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>BRENDAMORE10722@GMAIL.COM</t>
+          <t>ADJANIAVILA123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>16-02-2026 16:30:36</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 20:02:24</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>16-02-2026 16:31:54</t>
+          <t>09-02-2026 20:06:57</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>09-02-2026 20:05:35</t>
+        </is>
+      </c>
       <c r="U68" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W68" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9583,19 +9595,19 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26070522395700003497</t>
+          <t>26070522212990003013</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -9734,12 +9746,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>346873</t>
+          <t>343381</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>89038</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9749,17 +9761,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LUIS OSCAR</t>
+          <t>IVETTE CYNDEL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9769,39 +9781,35 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6645995563</t>
+          <t>6642061023</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>C LOMA BONITA  17205 H</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>16-07-1985</t>
+          <t>02-04-1988</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>LONUFER09@GMAIL.COM</t>
+          <t>CYNDEL08@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>27-02-2026 08:30:59</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 19:00:09</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9819,17 +9827,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>27-02-2026 08:45:08</t>
+          <t>12-02-2026 19:13:58</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>27-02-2026 08:43:02</t>
+          <t>12-02-2026 19:13:35</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -9849,7 +9857,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26070522706740004264</t>
+          <t>26070522304320003309</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
@@ -9873,12 +9881,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>343381</t>
+          <t>342675</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21198</t>
+          <t>20492</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9888,17 +9896,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>IVETTE CYNDEL</t>
+          <t>EDGAR OMAR</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MEJIA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9908,32 +9916,32 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6642061023</t>
+          <t>6647499507</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>02-04-1988</t>
+          <t>31-01-1991</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CYNDEL08@HOTMAIL.COM</t>
+          <t>RODRIGUEZEDGAR181@GMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>12-02-2026 19:00:09</t>
+          <t>10-02-2026 15:36:59</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9954,17 +9962,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>12-02-2026 19:13:58</t>
+          <t>10-02-2026 15:39:40</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>12-02-2026 19:13:35</t>
+          <t>10-02-2026 15:39:00</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -9974,7 +9982,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -9984,7 +9992,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26070522304320003309</t>
+          <t>26070522235030003086</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
@@ -9996,24 +10004,24 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>342675</t>
+          <t>344166</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>21983</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10023,17 +10031,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>EDGAR OMAR</t>
+          <t>BRENDA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MEJIA</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -10043,75 +10051,67 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>6647499507</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>RE</t>
-        </is>
-      </c>
+          <t>6651072660</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>31-01-1991</t>
+          <t>22-06-1999</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>RODRIGUEZEDGAR181@GMAIL.COM</t>
+          <t>BRENDAMORE10722@GMAIL.COM</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>10-02-2026 15:36:59</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>16-02-2026 16:30:36</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>10-02-2026 15:39:40</t>
+          <t>16-02-2026 16:31:54</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>10-02-2026 15:39:00</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10119,19 +10119,19 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>26070522235030003086</t>
+          <t>26070522395700003497</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -11080,12 +11080,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>346091</t>
+          <t>345876</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>88256</t>
+          <t>88041</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11095,17 +11095,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SANDY ERICKA</t>
+          <t>YANELY IZAMAR</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>LOZADA</t>
+          <t>ZACARIAS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -11115,14 +11115,10 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>6634232616</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
+          <t>6645810733</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -11130,64 +11126,56 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>31-10-1987</t>
+          <t>29-11-1994</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>SANDYKALETLOZADA@GMAIL.COM</t>
+          <t>ZACARIASYANELY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>24-02-2026 08:42:21</t>
+          <t>23-02-2026 16:35:07</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>24-02-2026 08:52:40</t>
+          <t>23-02-2026 16:36:42</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>24-02-2026 08:45:44</t>
-        </is>
-      </c>
+          <t>23-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11195,24 +11183,24 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>26070522613700003996</t>
+          <t>26070522587680003928</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -11358,12 +11346,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>344306</t>
+          <t>346009</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>22123</t>
+          <t>88174</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11373,17 +11361,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SYLVANNA</t>
+          <t>CESAR JESUS</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>LOYA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -11393,28 +11381,32 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>6642635718</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>6442591138</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>21-08-2014</t>
+          <t>29-08-1995</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>SYLVANNALOYACRUZ@GMAIL.COM</t>
+          <t>CESARJ3480@GMAIL.COM</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>16-02-2026 18:40:11</t>
+          <t>23-02-2026 18:57:52</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -11424,36 +11416,44 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>18-02-2026 16:43:12</t>
+          <t>23-02-2026 19:04:04</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:03:20</t>
+        </is>
+      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W82" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11461,40 +11461,36 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>26070522467040003667</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26070522598280003955</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>345876</t>
+          <t>346106</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>88041</t>
+          <t>88271</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11504,17 +11500,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>YANELY IZAMAR</t>
+          <t>JOSE DANIEL</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ZACARIAS</t>
+          <t>HIGUERA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -11524,33 +11520,33 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>6645810733</t>
+          <t>6644553643</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>29-11-1994</t>
+          <t>11-03-2008</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>ZACARIASYANELY@GMAIL.COM</t>
+          <t>ATMJARELLANODANIEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>23-02-2026 16:35:07</t>
+          <t>24-02-2026 09:42:40</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -11560,28 +11556,28 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>23-02-2026 16:36:42</t>
+          <t>24-02-2026 09:44:13</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V83" t="inlineStr"/>
@@ -11592,36 +11588,36 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>26070522587680003928</t>
+          <t>26070522615010004002</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>345113</t>
+          <t>344306</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>87278</t>
+          <t>22123</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11631,17 +11627,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE FRANCISCO </t>
+          <t>SYLVANNA</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SALDAÑA</t>
+          <t>LOYA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -11651,28 +11647,28 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>6631278884</t>
+          <t>6642635718</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>24-01-1996</t>
+          <t>21-08-2014</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>JOSESALDANA1996@ICLOUD.COM</t>
+          <t>SYLVANNALOYACRUZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>19-02-2026 15:57:19</t>
+          <t>16-02-2026 18:40:11</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -11697,18 +11693,18 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>19-02-2026 15:58:10</t>
+          <t>18-02-2026 16:43:12</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V84" t="inlineStr"/>
@@ -11719,10 +11715,14 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>26070522497920003762</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr"/>
+          <t>26070522467040003667</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr">
         <is>
@@ -11743,12 +11743,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>346009</t>
+          <t>346091</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>88174</t>
+          <t>88256</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11758,17 +11758,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CESAR JESUS</t>
+          <t>SANDY ERICKA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>LOZADA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>6442591138</t>
+          <t>6634232616</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -11788,57 +11788,57 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>29-08-1995</t>
+          <t>31-10-1987</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CESARJ3480@GMAIL.COM</t>
+          <t>SANDYKALETLOZADA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>23-02-2026 18:57:52</t>
+          <t>24-02-2026 08:42:21</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>23-02-2026 19:04:04</t>
+          <t>24-02-2026 08:52:40</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>23-02-2026 19:03:20</t>
+          <t>24-02-2026 08:45:44</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -11858,14 +11858,14 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>26070522598280003955</t>
+          <t>26070522613700003996</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
@@ -11882,12 +11882,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>346106</t>
+          <t>345113</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>88271</t>
+          <t>87278</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -11897,17 +11897,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>JOSE DANIEL</t>
+          <t xml:space="preserve">JOSE FRANCISCO </t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t>SALDAÑA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>HIGUERA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>6644553643</t>
+          <t>6631278884</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>11-03-2008</t>
+          <t>24-01-1996</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>ATMJARELLANODANIEL@GMAIL.COM</t>
+          <t>JOSESALDANA1996@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>24-02-2026 09:42:40</t>
+          <t>19-02-2026 15:57:19</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -11963,12 +11963,12 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>24-02-2026 09:44:13</t>
+          <t>19-02-2026 15:58:10</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>26070522615010004002</t>
+          <t>26070522497920003762</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr"/>
@@ -11997,24 +11997,24 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>345119</t>
+          <t>346079</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>87284</t>
+          <t>88244</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -12024,17 +12024,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEBASTIAN </t>
+          <t>OSCAR</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALVAREZ </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>6643203595</t>
+          <t>5546010096</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -12055,22 +12055,22 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>30-09-1999</t>
+          <t>24-01-1980</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>ALVAREZX19221@GMAIL.COM</t>
+          <t>OSCAR.MARTINEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>19-02-2026 16:07:14</t>
+          <t>24-02-2026 07:25:58</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -12090,18 +12090,18 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>19-02-2026 16:08:35</t>
+          <t>24-02-2026 07:26:50</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V87" t="inlineStr"/>
@@ -12112,7 +12112,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>26070522498190003763</t>
+          <t>26070522611470003990</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr"/>
@@ -12124,24 +12124,24 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>346079</t>
+          <t>346108</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>88244</t>
+          <t>88273</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -12151,17 +12151,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>OSCAR</t>
+          <t>DAVID SALVADOR</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>HIGUERA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>5546010096</t>
+          <t>6642947038</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -12182,17 +12182,17 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>24-01-1980</t>
+          <t>25-06-2010</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>OSCAR.MARTINEZ@GMAIL.COM</t>
+          <t>DARELLANOHIGUERA429@GMAIL.COM</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>24-02-2026 07:25:58</t>
+          <t>24-02-2026 09:47:39</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>24-02-2026 07:26:50</t>
+          <t>24-02-2026 09:48:32</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>26070522611470003990</t>
+          <t>26070522615140004003</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr"/>
@@ -12263,12 +12263,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>346108</t>
+          <t>345119</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>88273</t>
+          <t>87284</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -12278,17 +12278,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DAVID SALVADOR</t>
+          <t xml:space="preserve">SEBASTIAN </t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t xml:space="preserve">ALVAREZ </t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HIGUERA</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -12298,7 +12298,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>6642947038</t>
+          <t>6643203595</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -12309,22 +12309,22 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>25-06-2010</t>
+          <t>30-09-1999</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>DARELLANOHIGUERA429@GMAIL.COM</t>
+          <t>ALVAREZX19221@GMAIL.COM</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>24-02-2026 09:47:39</t>
+          <t>19-02-2026 16:07:14</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -12344,18 +12344,18 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>24-02-2026 09:48:32</t>
+          <t>19-02-2026 16:08:35</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V89" t="inlineStr"/>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>26070522615140004003</t>
+          <t>26070522498190003763</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr"/>
@@ -12378,12 +12378,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PAPALOTE TJ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PAPALOTE TJ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347297</t>
+          <t>347595</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89462</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HUGO RAUL</t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>MORGA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6646139028</t>
+          <t>6631222668</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OIJO</t>
+          <t>REFC</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -771,52 +771,52 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16-06-2001</t>
+          <t>11-05-1997</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>VALENZUELA6605@GMAIL.COM</t>
+          <t>PM0158415@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>01-03-2026 10:26:53</t>
+          <t>02-03-2026 14:35:39</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>01-03-2026 10:31:12</t>
+          <t>02-03-2026 14:39:15</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>01-03-2026 10:30:23</t>
+          <t>02-03-2026 14:38:50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -836,14 +836,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26070522766730004345</t>
+          <t>26070522795270004421</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -860,12 +860,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347595</t>
+          <t>347596</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89760</t>
+          <t>89761</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -875,17 +875,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>JOSUE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MORGA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6631222668</t>
+          <t>6648522578</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>REFC</t>
+          <t>RV</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -910,17 +910,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>11-05-1997</t>
+          <t>15-10-1997</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PM0158415@GMAIL.COM</t>
+          <t>JOSUEPEREZ89204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 14:35:39</t>
+          <t>02-03-2026 14:39:43</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 14:39:15</t>
+          <t>02-03-2026 14:50:12</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>02-03-2026 14:38:50</t>
+          <t>02-03-2026 14:42:34</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26070522795270004421</t>
+          <t>26070522795770004425</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -1126,24 +1126,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347797</t>
+          <t>348288</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89962</t>
+          <t>90453</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1153,17 +1153,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>HECTOR SAUL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BARRADAS</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1173,32 +1173,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6561309595</t>
+          <t>6642192653</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>25-03-1994</t>
+          <t>12-08-2001</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ELIZABETH.CBARRADAS@HOTMAIL.COM</t>
+          <t>HECTOR.SMD1281@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 18:11:42</t>
+          <t>03-03-2026 20:48:38</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 18:15:07</t>
+          <t>03-03-2026 20:51:55</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 18:14:46</t>
+          <t>03-03-2026 20:51:17</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26070522810970004458</t>
+          <t>26070522861580004626</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1277,12 +1277,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347596</t>
+          <t>348289</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89761</t>
+          <t>90454</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1292,17 +1292,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JOSUE</t>
+          <t xml:space="preserve">DULCE KARINA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1312,32 +1312,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6648522578</t>
+          <t>6647633676</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>RV</t>
+          <t>VCV</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>15-10-1997</t>
+          <t>09-03-2002</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JOSUEPEREZ89204@GMAIL.COM</t>
+          <t>DULCEKARINAIBAEEALEYVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 14:39:43</t>
+          <t>03-03-2026 20:49:06</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1362,17 +1362,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 14:50:12</t>
+          <t>03-03-2026 20:54:36</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-03-2026 14:42:34</t>
+          <t>03-03-2026 20:54:05</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26070522795770004425</t>
+          <t>26070522861670004628</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1416,12 +1416,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347921</t>
+          <t>347297</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90086</t>
+          <t>89462</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JULIAN ANTUAN</t>
+          <t>HUGO RAUL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1451,10 +1451,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6643714007</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6646139028</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>OIJO</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1462,56 +1466,64 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>04-11-2005</t>
+          <t>16-06-2001</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>VELAZQUEZ98ANTHUAN@GMAIL.COM</t>
+          <t>VALENZUELA6605@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 22:14:33</t>
+          <t>01-03-2026 10:26:53</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 22:15:48</t>
+          <t>01-03-2026 10:31:12</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:30:23</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1519,22 +1531,566 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26070522821220004509</t>
+          <t>26070522766730004345</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>347921</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>90086</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>JULIAN ANTUAN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SUAREZ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VELAZQUEZ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6643714007</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>04-11-2005</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>VELAZQUEZ98ANTHUAN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>02-03-2026 22:14:33</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>02-03-2026 22:15:48</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>26070522821220004509</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>347797</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>89962</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ELIZABETH</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BARRADAS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6561309595</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>25-03-1994</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ELIZABETH.CBARRADAS@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:11:42</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:15:07</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:14:46</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26070522810970004458</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Brenda Tania  Toriz Salazar</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>348211</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90376</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OMAR EDUARDO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>5574031355</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>FDC</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>11-10-1986</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>EDU_19TJ@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:08:17</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:11:01</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:10:30</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26070522853820004601</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>348212</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90377</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PABLO JAVIER</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GONZALEZ </t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6643475625</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>05-04-2005</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>PABLOJDIAZ9@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:08:31</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:12:47</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:12:21</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26070522853900004602</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PAPALOTE TJ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PAPALOTE TJ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347595</t>
+          <t>346881</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89760</t>
+          <t>89046</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>OSCAR DANIEL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MORGA</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -756,14 +756,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6631222668</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>REFC</t>
-        </is>
-      </c>
+          <t>6311379900</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -771,32 +767,32 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>11-05-1997</t>
+          <t>24-09-2005</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PM0158415@GMAIL.COM</t>
+          <t>OSCARDROMANR24@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 14:35:39</t>
+          <t>27-02-2026 09:00:08</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -806,29 +802,21 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 14:39:15</t>
+          <t>05-03-2026 07:59:02</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>02-03-2026 14:38:50</t>
-        </is>
-      </c>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -836,11 +824,19 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26070522795270004421</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>26070522909930004746</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>549</t>
@@ -848,24 +844,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347596</t>
+          <t>347436</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89761</t>
+          <t>89601</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -875,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JOSUE</t>
+          <t>NICOLE YAMILETH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,32 +891,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6648522578</t>
+          <t>6646577780</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RV</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>15-10-1997</t>
+          <t>06-10-2007</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>JOSUEPEREZ89204@GMAIL.COM</t>
+          <t>LAMAMAWUISKIS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 14:39:43</t>
+          <t>02-03-2026 08:12:50</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -945,17 +941,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 14:50:12</t>
+          <t>04-03-2026 10:42:55</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>02-03-2026 14:42:34</t>
+          <t>04-03-2026 10:42:26</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -975,11 +971,19 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26070522795770004425</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26070522878830004646</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Armando Figueroa  uribe</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>549</t>
@@ -987,24 +991,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347890</t>
+          <t>347297</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90055</t>
+          <t>89462</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1014,17 +1018,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DANNA PAOLA</t>
+          <t>HUGO RAUL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LAZARO</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1034,67 +1038,67 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6646322338</t>
+          <t>6646139028</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>OIJO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>15-11-2002</t>
+          <t>16-06-2001</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PAOLA1511FELIX@GMAIL.COM</t>
+          <t>VALENZUELA6605@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 19:59:10</t>
+          <t>01-03-2026 10:26:53</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 20:03:56</t>
+          <t>01-03-2026 10:31:12</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 20:03:07</t>
+          <t>01-03-2026 10:30:23</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1114,19 +1118,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26070522818630004499</t>
+          <t>26070522766730004345</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1138,12 +1142,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>348288</t>
+          <t>347596</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90453</t>
+          <t>89761</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1153,17 +1157,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HECTOR SAUL</t>
+          <t>JOSUE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1173,12 +1177,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6642192653</t>
+          <t>6648522578</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>RV</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1188,17 +1192,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>12-08-2001</t>
+          <t>15-10-1997</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>HECTOR.SMD1281@GMAIL.COM</t>
+          <t>JOSUEPEREZ89204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>03-03-2026 20:48:38</t>
+          <t>02-03-2026 14:39:43</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1223,17 +1227,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 20:51:55</t>
+          <t>02-03-2026 14:50:12</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>03-03-2026 20:51:17</t>
+          <t>02-03-2026 14:42:34</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1253,7 +1257,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26070522861580004626</t>
+          <t>26070522795770004425</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1265,24 +1269,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>348289</t>
+          <t>347435</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>89600</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1292,17 +1296,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DULCE KARINA </t>
+          <t>OLIVIA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>PIZARRO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1312,12 +1316,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6647633676</t>
+          <t>6642444818</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>VCV</t>
+          <t>C ARTESANOS</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1327,17 +1331,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>09-03-2002</t>
+          <t>03-06-1998</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>DULCEKARINAIBAEEALEYVA@GMAIL.COM</t>
+          <t>OLIVIAPIZARRO1998@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>03-03-2026 20:49:06</t>
+          <t>02-03-2026 08:12:02</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1362,17 +1366,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 20:54:36</t>
+          <t>04-03-2026 10:39:55</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>03-03-2026 20:54:05</t>
+          <t>04-03-2026 10:39:26</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1392,11 +1396,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26070522861670004628</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26070522878780004645</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Armando Figueroa  uribe</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>549</t>
@@ -1416,12 +1428,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347297</t>
+          <t>348289</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89462</t>
+          <t>90454</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1431,17 +1443,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HUGO RAUL</t>
+          <t xml:space="preserve">DULCE KARINA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1451,67 +1463,67 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6646139028</t>
+          <t>6647633676</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OIJO</t>
+          <t>VCV</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>16-06-2001</t>
+          <t>09-03-2002</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>VALENZUELA6605@GMAIL.COM</t>
+          <t>DULCEKARINAIBAEEALEYVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>01-03-2026 10:26:53</t>
+          <t>03-03-2026 20:49:06</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>01-03-2026 10:31:12</t>
+          <t>03-03-2026 20:54:36</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>01-03-2026 10:30:23</t>
+          <t>03-03-2026 20:54:05</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1531,36 +1543,36 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26070522766730004345</t>
+          <t>26070522861670004628</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347921</t>
+          <t>347797</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90086</t>
+          <t>89962</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1570,17 +1582,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JULIAN ANTUAN</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>BARRADAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1590,43 +1602,47 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6643714007</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6561309595</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>04-11-2005</t>
+          <t>25-03-1994</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>VELAZQUEZ98ANTHUAN@GMAIL.COM</t>
+          <t>ELIZABETH.CBARRADAS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 22:14:33</t>
+          <t>02-03-2026 18:11:42</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1636,7 +1652,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 22:15:48</t>
+          <t>02-03-2026 18:15:07</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1644,13 +1660,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:14:46</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1658,7 +1682,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26070522821220004509</t>
+          <t>26070522810970004458</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1670,24 +1694,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347797</t>
+          <t>347921</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89962</t>
+          <t>90086</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1697,17 +1721,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>JULIAN ANTUAN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BARRADAS</t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1717,47 +1741,43 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6561309595</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
+          <t>6643714007</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>25-03-1994</t>
+          <t>04-11-2005</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ELIZABETH.CBARRADAS@HOTMAIL.COM</t>
+          <t>VELAZQUEZ98ANTHUAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 18:11:42</t>
+          <t>02-03-2026 22:14:33</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1767,7 +1787,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 18:15:07</t>
+          <t>02-03-2026 22:15:48</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1775,21 +1795,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:14:46</t>
-        </is>
-      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1797,7 +1809,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26070522810970004458</t>
+          <t>26070522821220004509</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1809,7 +1821,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1948,12 +1960,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -2087,10 +2099,558 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>348288</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90453</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HECTOR SAUL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MACIAS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DUARTE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6642192653</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>9562</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>12-08-2001</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>HECTOR.SMD1281@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:48:38</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:51:55</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:51:17</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26070522861580004626</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>347595</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>89760</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LUIS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MORGA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6631222668</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>REFC</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>11-05-1997</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PM0158415@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>02-03-2026 14:35:39</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>02-03-2026 14:39:15</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>02-03-2026 14:38:50</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26070522795270004421</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>347890</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90055</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DANNA PAOLA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>FELIX</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>LAZARO</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6646322338</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>15-11-2002</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PAOLA1511FELIX@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:59:10</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:03:56</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:03:07</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26070522818630004499</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348574</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90739</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6643759766</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>03-10-1970</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PENDIRNEJDJK@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:43:05</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>04-03-2026 20:42:43</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26070522899730004730</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PAPALOTE TJ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PAPALOTE TJ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -856,12 +856,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347436</t>
+          <t>347297</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89601</t>
+          <t>89462</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NICOLE YAMILETH</t>
+          <t>HUGO RAUL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,67 +891,67 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6646577780</t>
+          <t>6646139028</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>OIJO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>06-10-2007</t>
+          <t>16-06-2001</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>LAMAMAWUISKIS@GMAIL.COM</t>
+          <t>VALENZUELA6605@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 08:12:50</t>
+          <t>01-03-2026 10:26:53</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>04-03-2026 10:42:55</t>
+          <t>01-03-2026 10:31:12</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>04-03-2026 10:42:26</t>
+          <t>01-03-2026 10:30:23</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -971,22 +971,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26070522878830004646</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Armando Figueroa  uribe</t>
-        </is>
-      </c>
+          <t>26070522766730004345</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1003,12 +995,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347297</t>
+          <t>347436</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89462</t>
+          <t>89601</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1018,17 +1010,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HUGO RAUL</t>
+          <t>NICOLE YAMILETH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1038,67 +1030,67 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6646139028</t>
+          <t>6646577780</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OIJO</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>16-06-2001</t>
+          <t>06-10-2007</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>VALENZUELA6605@GMAIL.COM</t>
+          <t>LAMAMAWUISKIS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>01-03-2026 10:26:53</t>
+          <t>02-03-2026 08:12:50</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>01-03-2026 10:31:12</t>
+          <t>04-03-2026 10:42:55</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>01-03-2026 10:30:23</t>
+          <t>04-03-2026 10:42:26</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1118,14 +1110,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26070522766730004345</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26070522878830004646</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Armando Figueroa  uribe</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1142,12 +1142,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347596</t>
+          <t>347595</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89761</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JOSUE</t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>MORGA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6648522578</t>
+          <t>6631222668</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RV</t>
+          <t>REFC</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1192,17 +1192,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>15-10-1997</t>
+          <t>11-05-1997</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>JOSUEPEREZ89204@GMAIL.COM</t>
+          <t>PM0158415@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 14:39:43</t>
+          <t>02-03-2026 14:35:39</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1227,17 +1227,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 14:50:12</t>
+          <t>02-03-2026 14:39:15</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 14:42:34</t>
+          <t>02-03-2026 14:38:50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26070522795770004425</t>
+          <t>26070522795270004421</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1281,12 +1281,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347435</t>
+          <t>347596</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89600</t>
+          <t>89761</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OLIVIA</t>
+          <t>JOSUE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PIZARRO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1316,32 +1316,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6642444818</t>
+          <t>6648522578</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C ARTESANOS</t>
+          <t>RV</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>03-06-1998</t>
+          <t>15-10-1997</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>OLIVIAPIZARRO1998@GMAIL.COM</t>
+          <t>JOSUEPEREZ89204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 08:12:02</t>
+          <t>02-03-2026 14:39:43</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1366,17 +1366,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>04-03-2026 10:39:55</t>
+          <t>02-03-2026 14:50:12</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>04-03-2026 10:39:26</t>
+          <t>02-03-2026 14:42:34</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1396,19 +1396,11 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26070522878780004645</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Armando Figueroa  uribe</t>
-        </is>
-      </c>
+          <t>26070522795770004425</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
           <t>549</t>
@@ -1416,24 +1408,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>348289</t>
+          <t>347435</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>89600</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1443,17 +1435,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DULCE KARINA </t>
+          <t>OLIVIA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>PIZARRO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1463,12 +1455,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6647633676</t>
+          <t>6642444818</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>VCV</t>
+          <t>C ARTESANOS</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1478,17 +1470,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>09-03-2002</t>
+          <t>03-06-1998</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>DULCEKARINAIBAEEALEYVA@GMAIL.COM</t>
+          <t>OLIVIAPIZARRO1998@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-03-2026 20:49:06</t>
+          <t>02-03-2026 08:12:02</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1513,7 +1505,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 20:54:36</t>
+          <t>04-03-2026 10:39:55</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1523,7 +1515,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>03-03-2026 20:54:05</t>
+          <t>04-03-2026 10:39:26</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1543,11 +1535,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26070522861670004628</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>26070522878780004645</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Armando Figueroa  uribe</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>549</t>
@@ -1555,24 +1555,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347797</t>
+          <t>347890</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89962</t>
+          <t>90055</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>DANNA PAOLA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BARRADAS</t>
+          <t>LAZARO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6561309595</t>
+          <t>6646322338</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1617,17 +1617,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>25-03-1994</t>
+          <t>15-11-2002</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ELIZABETH.CBARRADAS@HOTMAIL.COM</t>
+          <t>PAOLA1511FELIX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 18:11:42</t>
+          <t>02-03-2026 19:59:10</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1652,17 +1652,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 18:15:07</t>
+          <t>02-03-2026 20:03:56</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 18:14:46</t>
+          <t>02-03-2026 20:03:07</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26070522810970004458</t>
+          <t>26070522818630004499</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1833,12 +1833,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348211</t>
+          <t>348020</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90376</t>
+          <t>90185</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1848,17 +1848,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OMAR EDUARDO</t>
+          <t>EVELYN DAYANARA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>TORRESILLAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1868,47 +1868,43 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5574031355</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>FDC</t>
-        </is>
-      </c>
+          <t>6632140142</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>11-10-1986</t>
+          <t>30-10-1997</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>EDU_19TJ@HOTMAIL.COM</t>
+          <t>BARBOSAEVELYN333@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 18:08:17</t>
+          <t>03-03-2026 12:07:38</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1918,29 +1914,21 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 18:11:01</t>
+          <t>06-03-2026 16:13:25</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>03-03-2026 18:10:30</t>
-        </is>
-      </c>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1948,11 +1936,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26070522853820004601</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>26070522953740004885</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>549</t>
@@ -1960,24 +1956,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348212</t>
+          <t>347797</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90377</t>
+          <t>89962</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1987,17 +1983,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PABLO JAVIER</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>BARRADAS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2007,32 +2003,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6643475625</t>
+          <t>6561309595</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>05-04-2005</t>
+          <t>25-03-1994</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PABLOJDIAZ9@GMAIL.COM</t>
+          <t>ELIZABETH.CBARRADAS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-03-2026 18:08:31</t>
+          <t>02-03-2026 18:11:42</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2057,17 +2053,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 18:12:47</t>
+          <t>02-03-2026 18:15:07</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>03-03-2026 18:12:21</t>
+          <t>02-03-2026 18:14:46</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2087,7 +2083,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26070522853900004602</t>
+          <t>26070522810970004458</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2099,7 +2095,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2111,12 +2107,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348288</t>
+          <t>348574</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90453</t>
+          <t>90739</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2126,17 +2122,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HECTOR SAUL</t>
+          <t>BLANCA ESTELA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2146,57 +2142,53 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6642192653</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>9562</t>
-        </is>
-      </c>
+          <t>6643759766</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12-08-2001</t>
+          <t>03-10-1970</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>HECTOR.SMD1281@GMAIL.COM</t>
+          <t>PENDIRNEJDJK@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 20:48:38</t>
+          <t>04-03-2026 18:43:05</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 20:51:55</t>
+          <t>04-03-2026 20:42:43</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2204,21 +2196,13 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>03-03-2026 20:51:17</t>
-        </is>
-      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2226,36 +2210,40 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26070522861580004626</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+          <t>26070522899730004730</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347595</t>
+          <t>348288</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89760</t>
+          <t>90453</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2265,17 +2253,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>HECTOR SAUL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MORGA</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2285,12 +2273,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6631222668</t>
+          <t>6642192653</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>REFC</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2300,17 +2288,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>11-05-1997</t>
+          <t>12-08-2001</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PM0158415@GMAIL.COM</t>
+          <t>HECTOR.SMD1281@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 14:35:39</t>
+          <t>03-03-2026 20:48:38</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2335,7 +2323,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 14:39:15</t>
+          <t>03-03-2026 20:51:55</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2345,7 +2333,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-03-2026 14:38:50</t>
+          <t>03-03-2026 20:51:17</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2365,7 +2353,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26070522795270004421</t>
+          <t>26070522861580004626</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2389,12 +2377,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347890</t>
+          <t>348211</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90055</t>
+          <t>90376</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2404,17 +2392,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DANNA PAOLA</t>
+          <t>OMAR EDUARDO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LAZARO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2424,32 +2412,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6646322338</t>
+          <t>5574031355</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>15-11-2002</t>
+          <t>11-10-1986</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PAOLA1511FELIX@GMAIL.COM</t>
+          <t>EDU_19TJ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:59:10</t>
+          <t>03-03-2026 18:08:17</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2474,7 +2462,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 20:03:56</t>
+          <t>03-03-2026 18:11:01</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2484,7 +2472,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>02-03-2026 20:03:07</t>
+          <t>03-03-2026 18:10:30</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2504,7 +2492,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26070522818630004499</t>
+          <t>26070522853820004601</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2528,12 +2516,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348574</t>
+          <t>348212</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90739</t>
+          <t>90377</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2543,17 +2531,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BLANCA ESTELA</t>
+          <t>PABLO JAVIER</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2563,67 +2551,79 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6643759766</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>6643475625</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>03-10-1970</t>
+          <t>05-04-2005</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PENDIRNEJDJK@GMAIL.COM</t>
+          <t>PABLOJDIAZ9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>04-03-2026 18:43:05</t>
+          <t>03-03-2026 18:08:31</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>04-03-2026 20:42:43</t>
+          <t>03-03-2026 18:12:47</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:12:21</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2631,26 +2631,566 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26070522899730004730</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26070522853900004602</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>348706</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90871</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DANIELA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NORIS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6634309881</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>27-12-1998</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>DANIELA.NORIS27@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>05-03-2026 14:35:45</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>06-03-2026 15:02:17</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26070522951760004878</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>348289</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>90454</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DULCE KARINA </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>IBARRA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>LEYVA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6647633676</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>09-03-2002</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>DULCEKARINAIBAEEALEYVA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:49:06</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:54:36</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:54:05</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26070522861670004628</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>349157</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>91322</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GISELA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CHAVEZ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PRUDENTE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6648198159</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>C DE LOS MANZA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>08-01-1999</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>GISELA.PRUDENTE.2022@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:53:28</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:59:02</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:58:20</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26070522975890004938</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>349249</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>91414</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EMILIANO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CONTRERAS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6642382430</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>KMKL</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>16-08-2009</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>EMILLIANOAGUILARCONTRERAS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>08-03-2026 13:14:38</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>08-03-2026 13:19:15</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>07-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>08-03-2026 13:18:35</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26070522986890004946</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PAPALOTE TJ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PAPALOTE TJ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>346881</t>
+          <t>115550</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89046</t>
+          <t>13273</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OSCAR DANIEL</t>
+          <t>ANA LAURA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t>MOROYOQUI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -756,33 +756,37 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6311379900</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6643255588</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C. LOS ALAMOS </t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>24-09-2005</t>
+          <t>16-01-1997</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>OSCARDROMANR24@GMAIL.COM</t>
+          <t>MOROYOQUIZAVALA@EDU.UABC.MX</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>27-02-2026 09:00:08</t>
+          <t>12-08-2022 16:40:16</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -792,22 +796,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>05-03-2026 07:59:02</t>
+          <t>17-03-2026 18:31:55</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -824,44 +828,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26070522909930004746</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>TOMAS HERNANDEZ MARTINEZ</t>
-        </is>
-      </c>
+          <t>26070523266260005689</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347297</t>
+          <t>239282</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89462</t>
+          <t>36787</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HUGO RAUL</t>
+          <t xml:space="preserve">AYLIN </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">VILLAVICENCIO </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,32 +887,28 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6646139028</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>OIJO</t>
-        </is>
-      </c>
+          <t>6644986756</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>16-06-2001</t>
+          <t>25-09-1996</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>VALENZUELA6605@GMAIL.COM</t>
+          <t>AYLIN.2509@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>01-03-2026 10:26:53</t>
+          <t>11-06-2024 14:08:02</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -926,44 +918,36 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>01-03-2026 10:31:12</t>
+          <t>17-03-2026 07:12:22</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>31-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>01-03-2026 10:30:23</t>
-        </is>
-      </c>
+          <t>16-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -971,36 +955,36 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26070522766730004345</t>
+          <t>26120523244670011543</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347436</t>
+          <t>176478</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89601</t>
+          <t>73985</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1010,17 +994,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NICOLE YAMILETH</t>
+          <t>CRISTHIAN ALAIN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">OCHOA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t xml:space="preserve">CHAVEZ </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1030,47 +1014,43 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6646577780</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>SSD</t>
-        </is>
-      </c>
+          <t>6644207518</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>06-10-2007</t>
+          <t>09-06-2009</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>LAMAMAWUISKIS@GMAIL.COM</t>
+          <t>OCHOACHAVEZ@EDU.UABC.MX</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 08:12:50</t>
+          <t>13-06-2023 16:47:47</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1080,29 +1060,21 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>04-03-2026 10:42:55</t>
+          <t>13-03-2026 06:08:05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>04-03-2026 10:42:26</t>
-        </is>
-      </c>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1110,19 +1082,11 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26070522878830004646</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Armando Figueroa  uribe</t>
-        </is>
-      </c>
+          <t>26070523140370005413</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>549</t>
@@ -1130,24 +1094,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347595</t>
+          <t>266091</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89760</t>
+          <t>63595</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1157,17 +1121,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>ERICK ISRAEL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MORGA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1177,14 +1141,10 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6631222668</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>REFC</t>
-        </is>
-      </c>
+          <t>6647798010</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1192,64 +1152,56 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>11-05-1997</t>
+          <t>23-09-1997</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PM0158415@GMAIL.COM</t>
+          <t>ERIBOX316@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 14:35:39</t>
+          <t>13-11-2024 18:24:30</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 14:39:15</t>
+          <t>17-03-2026 20:44:18</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>02-03-2026 14:38:50</t>
-        </is>
-      </c>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1257,36 +1209,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26070522795270004421</t>
+          <t>26070523274320005716</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347596</t>
+          <t>259240</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89761</t>
+          <t>56744</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1296,17 +1248,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JOSUE</t>
+          <t>ADRIANA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1316,12 +1268,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6648522578</t>
+          <t>6643638028</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>RV</t>
+          <t>ANGELICA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1331,52 +1283,52 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>15-10-1997</t>
+          <t>26-05-1985</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JOSUEPEREZ89204@GMAIL.COM</t>
+          <t>ADRIANA.MENDOZA.ROD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 14:39:43</t>
+          <t>26-09-2024 19:03:44</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 14:50:12</t>
+          <t>18-03-2026 20:05:33</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>17-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-03-2026 14:42:34</t>
+          <t>18-03-2026 20:04:34</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1386,7 +1338,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1396,36 +1348,40 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26070522795770004425</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26110523308630005884</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347435</t>
+          <t>336910</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89600</t>
+          <t>22636</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1435,17 +1391,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OLIVIA</t>
+          <t>LESLIE ANGELICA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PIZARRO</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1455,12 +1411,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6642444818</t>
+          <t>6644511782</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C ARTESANOS</t>
+          <t>JIYUYJ</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1470,52 +1426,52 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>03-06-1998</t>
+          <t>25-05-1996</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>OLIVIAPIZARRO1998@GMAIL.COM</t>
+          <t>BELLACUENTOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 08:12:02</t>
+          <t>21-01-2026 20:31:16</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>04-03-2026 10:39:55</t>
+          <t>18-03-2026 22:36:45</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>17-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>04-03-2026 10:39:26</t>
+          <t>18-03-2026 22:35:42</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1535,22 +1491,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26070522878780004645</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Armando Figueroa  uribe</t>
-        </is>
-      </c>
+          <t>26070523311720005826</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1567,12 +1515,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347890</t>
+          <t>346881</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90055</t>
+          <t>89046</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1582,17 +1530,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DANNA PAOLA</t>
+          <t>OSCAR DANIEL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LAZARO</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1602,47 +1550,43 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6646322338</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>RE</t>
-        </is>
-      </c>
+          <t>6311379900</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15-11-2002</t>
+          <t>24-09-2005</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PAOLA1511FELIX@GMAIL.COM</t>
+          <t>OSCARDROMANR24@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 19:59:10</t>
+          <t>27-02-2026 09:00:08</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1652,29 +1596,21 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 20:03:56</t>
+          <t>05-03-2026 07:59:02</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>02-03-2026 20:03:07</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1682,11 +1618,19 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26070522818630004499</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26070522909930004746</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>549</t>
@@ -1694,7 +1638,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1706,12 +1650,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347921</t>
+          <t>347435</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90086</t>
+          <t>89600</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1721,17 +1665,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JULIAN ANTUAN</t>
+          <t>OLIVIA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>PIZARRO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1741,43 +1685,47 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6643714007</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6642444818</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>C ARTESANOS</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>04-11-2005</t>
+          <t>03-06-1998</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>VELAZQUEZ98ANTHUAN@GMAIL.COM</t>
+          <t>OLIVIAPIZARRO1998@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 22:14:33</t>
+          <t>02-03-2026 08:12:02</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1787,21 +1735,29 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 22:15:48</t>
+          <t>04-03-2026 10:39:55</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>04-03-2026 10:39:26</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1809,11 +1765,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26070522821220004509</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26070522878780004645</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Armando Figueroa  uribe</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>549</t>
@@ -1821,7 +1785,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1833,12 +1797,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348020</t>
+          <t>347436</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90185</t>
+          <t>89601</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1848,17 +1812,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EVELYN DAYANARA</t>
+          <t>NICOLE YAMILETH</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BARBOSA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TORRESILLAS</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1868,10 +1832,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6632140142</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6646577780</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1879,32 +1847,32 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>30-10-1997</t>
+          <t>06-10-2007</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>BARBOSAEVELYN333@GMAIL.COM</t>
+          <t>LAMAMAWUISKIS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 12:07:38</t>
+          <t>02-03-2026 08:12:50</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1914,21 +1882,29 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>06-03-2026 16:13:25</t>
+          <t>04-03-2026 10:42:55</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>04-03-2026 10:42:26</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1936,7 +1912,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26070522953740004885</t>
+          <t>26070522878830004646</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1946,7 +1922,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>TOMAS HERNANDEZ MARTINEZ</t>
+          <t>Armando Figueroa  uribe</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1956,24 +1932,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347797</t>
+          <t>346469</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89962</t>
+          <t>88634</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1983,17 +1959,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>JINHONG</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>FENG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BARRADAS</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2003,47 +1979,43 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6561309595</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
+          <t>6631240389</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>25-03-1994</t>
+          <t>17-01-1988</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ELIZABETH.CBARRADAS@HOTMAIL.COM</t>
+          <t>NOTIENHADSKJAM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 18:11:42</t>
+          <t>25-02-2026 13:22:14</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2053,29 +2025,21 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 18:15:07</t>
+          <t>18-03-2026 19:56:55</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:14:46</t>
-        </is>
-      </c>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2083,10 +2047,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26070522810970004458</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+          <t>26070523308170005809</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2095,24 +2063,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348574</t>
+          <t>347595</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90739</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2122,17 +2090,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BLANCA ESTELA</t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MORGA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2142,67 +2110,79 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6643759766</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6631222668</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>REFC</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>03-10-1970</t>
+          <t>11-05-1997</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PENDIRNEJDJK@GMAIL.COM</t>
+          <t>PM0158415@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>04-03-2026 18:43:05</t>
+          <t>02-03-2026 14:35:39</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>04-03-2026 20:42:43</t>
+          <t>02-03-2026 14:39:15</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>02-03-2026 14:38:50</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2210,40 +2190,36 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26070522899730004730</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26070522795270004421</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348288</t>
+          <t>347596</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90453</t>
+          <t>89761</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2253,17 +2229,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HECTOR SAUL</t>
+          <t>JOSUE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2273,12 +2249,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6642192653</t>
+          <t>6648522578</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>RV</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2288,17 +2264,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12-08-2001</t>
+          <t>15-10-1997</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>HECTOR.SMD1281@GMAIL.COM</t>
+          <t>JOSUEPEREZ89204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-03-2026 20:48:38</t>
+          <t>02-03-2026 14:39:43</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2323,17 +2299,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 20:51:55</t>
+          <t>02-03-2026 14:50:12</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>03-03-2026 20:51:17</t>
+          <t>02-03-2026 14:42:34</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2353,7 +2329,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26070522861580004626</t>
+          <t>26070522795770004425</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2377,12 +2353,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348211</t>
+          <t>347297</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90376</t>
+          <t>89462</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2392,17 +2368,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OMAR EDUARDO</t>
+          <t>HUGO RAUL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2412,12 +2388,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5574031355</t>
+          <t>6646139028</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>OIJO</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2427,52 +2403,52 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11-10-1986</t>
+          <t>16-06-2001</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>EDU_19TJ@HOTMAIL.COM</t>
+          <t>VALENZUELA6605@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 18:08:17</t>
+          <t>01-03-2026 10:26:53</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 18:11:01</t>
+          <t>01-03-2026 10:31:12</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>03-03-2026 18:10:30</t>
+          <t>01-03-2026 10:30:23</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2492,19 +2468,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26070522853820004601</t>
+          <t>26070522766730004345</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2516,12 +2492,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348212</t>
+          <t>347890</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90377</t>
+          <t>90055</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2531,17 +2507,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PABLO JAVIER</t>
+          <t>DANNA PAOLA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>LAZARO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2551,32 +2527,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6643475625</t>
+          <t>6646322338</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>05-04-2005</t>
+          <t>15-11-2002</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PABLOJDIAZ9@GMAIL.COM</t>
+          <t>PAOLA1511FELIX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 18:08:31</t>
+          <t>02-03-2026 19:59:10</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2601,17 +2577,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 18:12:47</t>
+          <t>02-03-2026 20:03:56</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>03-03-2026 18:12:21</t>
+          <t>02-03-2026 20:03:07</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2631,7 +2607,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26070522853900004602</t>
+          <t>26070522818630004499</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2655,12 +2631,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348706</t>
+          <t>347797</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90871</t>
+          <t>89962</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2670,17 +2646,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DANIELA</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NORIS</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>BARRADAS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2690,10 +2666,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6634309881</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6561309595</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2701,32 +2681,32 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>27-12-1998</t>
+          <t>25-03-1994</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>DANIELA.NORIS27@GMAIL.COM</t>
+          <t>ELIZABETH.CBARRADAS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>05-03-2026 14:35:45</t>
+          <t>02-03-2026 18:11:42</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2736,21 +2716,29 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>06-03-2026 15:02:17</t>
+          <t>02-03-2026 18:15:07</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:14:46</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2758,7 +2746,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26070522951760004878</t>
+          <t>26070522810970004458</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2770,24 +2758,24 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348289</t>
+          <t>347921</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>90086</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2797,17 +2785,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DULCE KARINA </t>
+          <t>JULIAN ANTUAN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2817,47 +2805,43 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6647633676</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>VCV</t>
-        </is>
-      </c>
+          <t>6643714007</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>09-03-2002</t>
+          <t>04-11-2005</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>DULCEKARINAIBAEEALEYVA@GMAIL.COM</t>
+          <t>VELAZQUEZ98ANTHUAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 20:49:06</t>
+          <t>02-03-2026 22:14:33</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2867,29 +2851,21 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-03-2026 20:54:36</t>
+          <t>02-03-2026 22:15:48</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>03-03-2026 20:54:05</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2897,7 +2873,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26070522861670004628</t>
+          <t>26070522821220004509</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2921,12 +2897,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>349157</t>
+          <t>348020</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>91322</t>
+          <t>90185</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2936,17 +2912,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GISELA</t>
+          <t>EVELYN DAYANARA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PRUDENTE</t>
+          <t>TORRESILLAS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2956,14 +2932,10 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6648198159</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>C DE LOS MANZA</t>
-        </is>
-      </c>
+          <t>6632140142</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2971,32 +2943,32 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>08-01-1999</t>
+          <t>30-10-1997</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>GISELA.PRUDENTE.2022@GMAIL.COM</t>
+          <t>BARBOSAEVELYN333@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>07-03-2026 13:53:28</t>
+          <t>03-03-2026 12:07:38</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -3006,29 +2978,21 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>07-03-2026 13:59:02</t>
+          <t>06-03-2026 16:13:25</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>07-03-2026 13:58:20</t>
-        </is>
-      </c>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3036,11 +3000,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26070522975890004938</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>26070522953740004885</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>549</t>
@@ -3060,12 +3032,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>349249</t>
+          <t>348211</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>91414</t>
+          <t>90376</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3075,7 +3047,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EMILIANO</t>
+          <t>OMAR EDUARDO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3085,7 +3057,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3095,12 +3067,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6642382430</t>
+          <t>5574031355</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>KMKL</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3110,17 +3082,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>16-08-2009</t>
+          <t>11-10-1986</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>EMILLIANOAGUILARCONTRERAS@GMAIL.COM</t>
+          <t>EDU_19TJ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>08-03-2026 13:14:38</t>
+          <t>03-03-2026 18:08:17</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3145,17 +3117,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>08-03-2026 13:19:15</t>
+          <t>03-03-2026 18:11:01</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>07-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>08-03-2026 13:18:35</t>
+          <t>03-03-2026 18:10:30</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3165,7 +3137,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3175,7 +3147,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26070522986890004946</t>
+          <t>26070522853820004601</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3187,10 +3159,4592 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>348212</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>90377</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PABLO JAVIER</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GONZALEZ </t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6643475625</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>05-04-2005</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PABLOJDIAZ9@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:08:31</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:12:47</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:12:21</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26070522853900004602</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>348600</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>90765</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ALICIA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DELGADILLO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NEVAREZ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6642840914</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>PANFILO NATERA 5818</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>18-05-1987</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>ALEJA92_64@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>04-03-2026 20:39:25</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>09-03-2026 11:56:48</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>09-03-2026 11:55:41</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26070523005070004989</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>IVAN ALBERTO NUÑEZ SANCHEZ</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>348706</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>90871</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DANIELA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NORIS</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6634309881</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>27-12-1998</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DANIELA.NORIS27@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>05-03-2026 14:35:45</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>06-03-2026 15:02:17</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26070522951760004878</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>348288</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>90453</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HECTOR SAUL</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MACIAS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DUARTE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6642192653</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>9562</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>12-08-2001</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>HECTOR.SMD1281@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:48:38</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:51:55</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:51:17</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26070522861580004626</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>348574</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>90739</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6643759766</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>03-10-1970</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>PENDIRNEJDJK@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:43:05</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>04-03-2026 20:42:43</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26070522899730004730</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>348289</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>90454</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DULCE KARINA </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>IBARRA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>LEYVA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6647633676</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>09-03-2002</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>DULCEKARINAIBAEEALEYVA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:49:06</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:54:36</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:54:05</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26070522861670004628</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>348769</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>90934</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DAVID</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>URIARTE</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PARRA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6674212830</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>23-06-2010</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>DAVID.URIARTEP23@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:34:58</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:49:12</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26070523019250005037</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>349335</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>91500</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ANGEL IGNACIO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6631126650</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>C DIRECCION DEL TRABAJO 15700</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>07-02-2002</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>IGNACIOCASTRO124@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>09-03-2026 09:28:48</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>09-03-2026 09:41:11</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>09-03-2026 09:35:16</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26070523002390004979</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>349460</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>91625</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ITZEL GABRIELA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>CORTEZ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6641717434</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>11-05-2000</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>CORTEZITZEL886@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:46:28</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:49:57</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:49:23</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26070523009930005018</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>348579</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>90744</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OLIVIA </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PARRA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>LIZARRAGA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6673906676</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>REFDC</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>04-06-2010</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>PARRAOLIVIA459@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:53:57</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:57:17</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:56:24</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26070523020030005043</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>KIMBERLY MICHEL ROMERO  BRITO</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>349440</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>91605</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FERNANDA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ESPINOZA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SANTILLANES</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6634037703</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>26-09-2009</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>FERNANDA.ESPINOZA2627@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:13:43</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:14:23</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26070523008620004997</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>349760</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>91925</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>YURI</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6199881225</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>25-12-1988</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>YURIGONZALEZ2506@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>10-03-2026 08:00:07</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>12-03-2026 08:03:33</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26070523117120005330</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>349157</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>91322</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>GISELA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CHAVEZ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PRUDENTE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6648198159</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>C DE LOS MANZA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>08-01-1999</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>GISELA.PRUDENTE.2022@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:53:28</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:59:02</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:58:20</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26070522975890004938</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>349249</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>91414</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>EMILIANO</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CONTRERAS</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6642382430</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>KMKL</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>16-08-2009</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>EMILLIANOAGUILARCONTRERAS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>08-03-2026 13:14:38</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>08-03-2026 13:19:15</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>07-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>08-03-2026 13:18:35</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26070522986890004946</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>349711</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>91876</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CARRILLO</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ALVA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6644383790</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>REFVC</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>10-03-1984</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>JUAN_CARRILLO85@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:15:18</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>13-03-2026 21:19:57</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>13-03-2026 21:19:22</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26070523165650005470</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>349929</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>92094</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PAOLA YANELY</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ARMENTA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>BELTRAN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6643308000</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>27-04-1981</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>LIAYOMARAPAO1503@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:05:51</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:12:15</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:10:50</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26070523062780005181</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>349445</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>91610</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ALMA JUDITH</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6645194747</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>17-04-1993</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>JUDITH.LG.0493@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:20:45</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:21:56</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26070523008840004998</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>349637</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>91802</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PRECIADO</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6645943269</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>PRIV BOURGES</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>23-01-2002</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>SEBASTIANPRECIADOAGUILAR@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:57:23</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:03:51</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:03:12</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26070523025520005064</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>349840</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>92005</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CARLOS</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ROMO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>BARAJAS</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6642252510</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>29-10-1983</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>ROMOBARAJASCARLOS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>10-03-2026 13:49:19</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>19-03-2026 14:02:57</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26070523328620005847</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>349931</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>92096</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ESPERANZA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ARAGON</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ROJAS</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6643704380</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>RES</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>20-02-1972</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>ESPE2020@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:06:52</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:25:11</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:14:53</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26070523063930005184</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>349439</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>91604</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>JAKELYN ALEXANDRA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANCHEZ </t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6631634914</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>30-12-2009</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>JAKELYNSG@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:12:00</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:12:40</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26070523008550004996</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>349735</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>91900</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>RAFAEL LEONARDO</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>GASCA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>OSORIO</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6647518542</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>11-10-1996</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>LEOGASCA158@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>09-03-2026 21:20:58</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>09-03-2026 21:23:29</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26070523033690005092</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>350349</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>92513</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>KARINA VANESSA</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>GAYTAN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>VERDUGO</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6198165722</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>27-11-1996</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>KARINA.GAYTAN11271996@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:45:22</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:08:40</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26070523232220005584</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>350158</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>92323</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>STEVEN</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LIU</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>HEU</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6646935482</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>11-03-2011</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>STEVENLIU110327@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>11-03-2026 16:50:12</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>18-03-2026 16:08:45</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26070523295830005778</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>350660</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>92824</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DIONE XARENY</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AVENDAÑO</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ROBLEZ</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6646141928</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>28-09-2000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>ROBLEZCYNTHIA12@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>13-03-2026 18:41:24</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>13-03-2026 18:45:31</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26070523161560005460</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>349956</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>92121</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>JULIANA SARAI</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>CORONA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6642204712</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>09-07-1984</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>J.CRUZC@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:36:28</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:37:53</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26070523064960005192</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>350608</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>92772</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BRYAN</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>MELENDEZ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>HIDALGO</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6634041120</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>REV</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>22-04-2004</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>ORK4N080@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>13-03-2026 16:15:29</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>13-03-2026 16:18:46</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>13-03-2026 16:18:13</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26070523156120005441</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>351439</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>93603</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VIANNEY GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ASTORGA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>AMARO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6647304532</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>DE LOS DURAZNOS 9314 19 D</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>04-08-2002</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>VIANNEY408PRINCESITA@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:34:14</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:44:53</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:43:53</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26070523248630005615</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>351349</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>93513</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>MAYTEE IRASEMA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>MUÑOZ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>AVENDAÑO</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6648958715</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>HJG</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>13-10-1999</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>MAYTEE.MUNOZ@OUTLOOK.ES</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:47:45</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>16-03-2026 20:32:12</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:50:20</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26070523235290005589</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>351025</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>93189</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HECTOR HELIO </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>6642926962</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>12-09-1981</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>HECSAN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>16-03-2026 09:21:21</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>16-03-2026 09:30:45</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>16-03-2026 09:30:07</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26070523212510005534</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>352018</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>94182</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MARIA GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>MATUZ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6442219951</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>08-09-1995</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>MATUZ2812@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>18-03-2026 21:13:15</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>18-03-2026 21:14:08</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26070523311000005823</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>351354</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>93518</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVA SAMANTHA </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>CORNEJO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>AVENDAÑO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>6634424337</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>22-09-2006</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>SAMANTHA.PRIV76@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:52:38</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:53:37</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26070523234150005586</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>351528</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>93692</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BERNAL</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6631044272</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>FTG</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>05-05-1998</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>LUISBERNAL050598@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>17-03-2026 14:47:29</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>17-03-2026 14:50:58</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>17-03-2026 14:50:25</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26070523255000005652</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Cesar Ivan Hernandez Garcia</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>351531</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>93695</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JESSY JISSELY </t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>BOJORQUEZ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>BERNAL</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6647268756</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>FDV</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>02-07-1997</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>JESSY.BOJORQUEZ.B1@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>17-03-2026 14:54:16</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>17-03-2026 14:57:05</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>17-03-2026 14:56:43</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26070523255210005653</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PAPALOTE TJ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PAPALOTE TJ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>333187</t>
+          <t>115550</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>13273</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ANA LIZBETH</t>
+          <t>ANA LAURA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLASCENCIA </t>
+          <t>MOROYOQUI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ROBLEDO</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6644918661</t>
+          <t>6643879271</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IFEL 2761 29</t>
+          <t xml:space="preserve">C. LOS ALAMOS </t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,64 +628,56 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>13-04-1986</t>
+          <t>16-01-1997</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PENDIENTEPORREGISTRAR@GMAIL.COM</t>
+          <t>MOROYOQUIZAVALA@EDU.UABC.MX</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>08-01-2026 17:43:35</t>
+          <t>12-08-2022 16:40:16</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 18:00:31</t>
+          <t>17-03-2026 18:31:55</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:59:46</t>
-        </is>
-      </c>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,40 +685,36 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26070522809710004449</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26070523266260005689</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>115550</t>
+          <t>239282</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>36787</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -736,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ANA LAURA</t>
+          <t xml:space="preserve">AYLIN </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MOROYOQUI</t>
+          <t xml:space="preserve">VILLAVICENCIO </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ZAVALA</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -756,14 +744,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6643255588</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C. LOS ALAMOS </t>
-        </is>
-      </c>
+          <t>6644986756</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -771,17 +755,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16-01-1997</t>
+          <t>25-09-1996</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MOROYOQUIZAVALA@EDU.UABC.MX</t>
+          <t>AYLIN.2509@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12-08-2022 16:40:16</t>
+          <t>11-06-2024 14:08:02</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -796,22 +780,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>17-03-2026 18:31:55</t>
+          <t>17-03-2026 07:12:22</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>16-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -828,36 +812,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26070523266260005689</t>
+          <t>26120523244670011543</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>239282</t>
+          <t>276983</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>36787</t>
+          <t>74484</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +851,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AYLIN </t>
+          <t>KEVIN JOVANNI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLAVICENCIO </t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>PRECIADO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,67 +871,75 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6644986756</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6645650966</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C DEL EBANO 25652 6 B </t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>25-09-1996</t>
+          <t>16-10-1999</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>AYLIN.2509@HOTMAIL.COM</t>
+          <t>KEVINPRECIADO084@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>11-06-2024 14:08:02</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2025 13:47:08</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17-03-2026 07:12:22</t>
+          <t>30-03-2026 06:55:34</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>16-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>30-03-2026 06:54:52</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -955,14 +947,18 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26120523244670011543</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
+          <t>26070523617670006587</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1094,24 +1090,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>266091</t>
+          <t>333187</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>63595</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1121,17 +1117,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ERICK ISRAEL</t>
+          <t>ANA LIZBETH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t xml:space="preserve">PLASCENCIA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>ROBLEDO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1141,67 +1137,79 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6647798010</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6644918661</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>IFEL 2761 29</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>23-09-1997</t>
+          <t>13-04-1986</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ERIBOX316@GMAIL.COM</t>
+          <t>PENDIENTEPORREGISTRAR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>13-11-2024 18:24:30</t>
+          <t>08-01-2026 17:43:35</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>17-03-2026 20:44:18</t>
+          <t>02-03-2026 18:00:31</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:59:46</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1209,14 +1217,18 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26070523274320005716</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+          <t>26070522809710004449</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1376,12 +1388,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>336910</t>
+          <t>266091</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22636</t>
+          <t>63595</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1391,17 +1403,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LESLIE ANGELICA</t>
+          <t>ERICK ISRAEL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1411,32 +1423,28 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6644511782</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>JIYUYJ</t>
-        </is>
-      </c>
+          <t>6647798010</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>25-05-1996</t>
+          <t>23-09-1997</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>BELLACUENTOS@GMAIL.COM</t>
+          <t>ERIBOX316@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>21-01-2026 20:31:16</t>
+          <t>13-11-2024 18:24:30</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1446,44 +1454,36 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>18-03-2026 22:36:45</t>
+          <t>17-03-2026 20:44:18</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>18-03-2026 22:35:42</t>
-        </is>
-      </c>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1491,36 +1491,36 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26070523311720005826</t>
+          <t>26070523274320005716</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>346881</t>
+          <t>347436</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89046</t>
+          <t>89601</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1530,17 +1530,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OSCAR DANIEL</t>
+          <t>NICOLE YAMILETH</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1550,43 +1550,47 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6311379900</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6646577780</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>24-09-2005</t>
+          <t>06-10-2007</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>OSCARDROMANR24@GMAIL.COM</t>
+          <t>LAMAMAWUISKIS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>27-02-2026 09:00:08</t>
+          <t>02-03-2026 08:12:50</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1596,21 +1600,29 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>05-03-2026 07:59:02</t>
+          <t>04-03-2026 10:42:55</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>04-03-2026 10:42:26</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1618,7 +1630,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26070522909930004746</t>
+          <t>26070522878830004646</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1628,7 +1640,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>TOMAS HERNANDEZ MARTINEZ</t>
+          <t>Armando Figueroa  uribe</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1797,12 +1809,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347436</t>
+          <t>336910</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89601</t>
+          <t>22636</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1812,17 +1824,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NICOLE YAMILETH</t>
+          <t>LESLIE ANGELICA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1832,12 +1844,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6646577780</t>
+          <t>6644511782</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>JIYUYJ</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1847,52 +1859,52 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>06-10-2007</t>
+          <t>25-05-1996</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>LAMAMAWUISKIS@GMAIL.COM</t>
+          <t>BELLACUENTOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 08:12:50</t>
+          <t>21-01-2026 20:31:16</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>04-03-2026 10:42:55</t>
+          <t>18-03-2026 22:36:45</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>17-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>04-03-2026 10:42:26</t>
+          <t>18-03-2026 22:35:42</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1912,27 +1924,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26070522878830004646</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Armando Figueroa  uribe</t>
-        </is>
-      </c>
+          <t>26070523311720005826</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1944,12 +1948,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>346469</t>
+          <t>346881</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>88634</t>
+          <t>89046</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1959,17 +1963,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JINHONG</t>
+          <t>OSCAR DANIEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FENG</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1979,7 +1983,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6631240389</t>
+          <t>6311379900</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1990,17 +1994,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>17-01-1988</t>
+          <t>24-09-2005</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>NOTIENHADSKJAM@GMAIL.COM</t>
+          <t>OSCARDROMANR24@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>25-02-2026 13:22:14</t>
+          <t>27-02-2026 09:00:08</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2025,12 +2029,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>18-03-2026 19:56:55</t>
+          <t>05-03-2026 07:59:02</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2047,15 +2051,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26070523308170005809</t>
+          <t>26070522909930004746</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>549</t>
@@ -2063,24 +2071,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347595</t>
+          <t>346469</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89760</t>
+          <t>88634</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2090,17 +2098,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>JINHONG</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>FENG</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MORGA</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2110,14 +2118,10 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6631222668</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>REFC</t>
-        </is>
-      </c>
+          <t>6631240389</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2125,32 +2129,32 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11-05-1997</t>
+          <t>17-01-1988</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PM0158415@GMAIL.COM</t>
+          <t>NOTIENHADSKJAM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 14:35:39</t>
+          <t>25-02-2026 13:22:14</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2160,29 +2164,21 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 14:39:15</t>
+          <t>18-03-2026 19:56:55</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>02-03-2026 14:38:50</t>
-        </is>
-      </c>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2190,10 +2186,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26070522795270004421</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+          <t>26070523308170005809</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347297</t>
+          <t>347595</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89462</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HUGO RAUL</t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>MORGA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6646139028</t>
+          <t>6631222668</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>OIJO</t>
+          <t>REFC</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2403,52 +2403,52 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>16-06-2001</t>
+          <t>11-05-1997</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>VALENZUELA6605@GMAIL.COM</t>
+          <t>PM0158415@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>01-03-2026 10:26:53</t>
+          <t>02-03-2026 14:35:39</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>01-03-2026 10:31:12</t>
+          <t>02-03-2026 14:39:15</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>31-03-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>01-03-2026 10:30:23</t>
+          <t>02-03-2026 14:38:50</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2468,19 +2468,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26070522766730004345</t>
+          <t>26070522795270004421</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2492,12 +2492,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347890</t>
+          <t>347921</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90055</t>
+          <t>90086</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2507,17 +2507,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DANNA PAOLA</t>
+          <t>JULIAN ANTUAN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LAZARO</t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2527,47 +2527,43 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6646322338</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>RE</t>
-        </is>
-      </c>
+          <t>6643714007</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>15-11-2002</t>
+          <t>04-11-2005</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PAOLA1511FELIX@GMAIL.COM</t>
+          <t>VELAZQUEZ98ANTHUAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 19:59:10</t>
+          <t>02-03-2026 22:14:33</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2577,7 +2573,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 20:03:56</t>
+          <t>02-03-2026 22:15:48</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2585,21 +2581,13 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>02-03-2026 20:03:07</t>
-        </is>
-      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2607,7 +2595,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26070522818630004499</t>
+          <t>26070522821220004509</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2631,12 +2619,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347797</t>
+          <t>348020</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89962</t>
+          <t>90185</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2646,17 +2634,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>EVELYN DAYANARA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>BARBOSA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BARRADAS</t>
+          <t>TORRESILLAS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2666,14 +2654,10 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6561309595</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
+          <t>6632140142</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2681,32 +2665,32 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>25-03-1994</t>
+          <t>30-10-1997</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ELIZABETH.CBARRADAS@HOTMAIL.COM</t>
+          <t>BARBOSAEVELYN333@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 18:11:42</t>
+          <t>03-03-2026 12:07:38</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2716,29 +2700,21 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 18:15:07</t>
+          <t>06-03-2026 16:13:25</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:14:46</t>
-        </is>
-      </c>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2746,11 +2722,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26070522810970004458</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26070522953740004885</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>549</t>
@@ -2758,7 +2742,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Brenda Tania  Toriz Salazar</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2770,12 +2754,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347921</t>
+          <t>347297</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90086</t>
+          <t>89462</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2785,17 +2769,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JULIAN ANTUAN</t>
+          <t>HUGO RAUL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2805,10 +2789,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6643714007</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6646139028</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>OIJO</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2816,56 +2804,64 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>04-11-2005</t>
+          <t>16-06-2001</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>VELAZQUEZ98ANTHUAN@GMAIL.COM</t>
+          <t>VALENZUELA6605@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 22:14:33</t>
+          <t>01-03-2026 10:26:53</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 22:15:48</t>
+          <t>01-03-2026 10:31:12</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>31-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:30:23</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2873,19 +2869,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26070522821220004509</t>
+          <t>26070522766730004345</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2897,12 +2893,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348020</t>
+          <t>347890</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90185</t>
+          <t>90055</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2912,17 +2908,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EVELYN DAYANARA</t>
+          <t>DANNA PAOLA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BARBOSA</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TORRESILLAS</t>
+          <t>LAZARO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2932,10 +2928,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6632140142</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6646322338</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2943,32 +2943,32 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>30-10-1997</t>
+          <t>15-11-2002</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BARBOSAEVELYN333@GMAIL.COM</t>
+          <t>PAOLA1511FELIX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-03-2026 12:07:38</t>
+          <t>02-03-2026 19:59:10</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2978,21 +2978,29 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>06-03-2026 16:13:25</t>
+          <t>02-03-2026 20:03:56</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:03:07</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3000,19 +3008,11 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26070522953740004885</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>TOMAS HERNANDEZ MARTINEZ</t>
-        </is>
-      </c>
+          <t>26070522818630004499</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
           <t>549</t>
@@ -3020,24 +3020,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348211</t>
+          <t>348574</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90376</t>
+          <t>90739</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3047,17 +3047,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OMAR EDUARDO</t>
+          <t>BLANCA ESTELA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3067,79 +3067,67 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5574031355</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>FDC</t>
-        </is>
-      </c>
+          <t>6643759766</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>11-10-1986</t>
+          <t>03-10-1970</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>EDU_19TJ@HOTMAIL.COM</t>
+          <t>PENDIRNEJDJK@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>03-03-2026 18:08:17</t>
+          <t>04-03-2026 18:43:05</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03-03-2026 18:11:01</t>
+          <t>04-03-2026 20:42:43</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>03-03-2026 18:10:30</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3147,19 +3135,23 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26070522853820004601</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
+          <t>26070522899730004730</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3171,12 +3163,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348212</t>
+          <t>348289</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90377</t>
+          <t>90454</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3186,17 +3178,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PABLO JAVIER</t>
+          <t xml:space="preserve">DULCE KARINA </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3206,32 +3198,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6643475625</t>
+          <t>6647633676</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>VCV</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>05-04-2005</t>
+          <t>09-03-2002</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>PABLOJDIAZ9@GMAIL.COM</t>
+          <t>DULCEKARINAIBAEEALEYVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>03-03-2026 18:08:31</t>
+          <t>03-03-2026 20:49:06</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3256,7 +3248,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-03-2026 18:12:47</t>
+          <t>03-03-2026 20:54:36</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3266,7 +3258,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>03-03-2026 18:12:21</t>
+          <t>03-03-2026 20:54:05</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3286,7 +3278,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26070522853900004602</t>
+          <t>26070522861670004628</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3310,12 +3302,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>348600</t>
+          <t>349335</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90765</t>
+          <t>91500</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3325,17 +3317,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ALICIA ALEJANDRA</t>
+          <t>ANGEL IGNACIO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>DELGADILLO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NEVAREZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3345,57 +3337,57 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6642840914</t>
+          <t>6631126650</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PANFILO NATERA 5818</t>
+          <t>C DIRECCION DEL TRABAJO 15700</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18-05-1987</t>
+          <t>07-02-2002</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ALEJA92_64@HOTMAIL.COM</t>
+          <t>IGNACIOCASTRO124@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>04-03-2026 20:39:25</t>
+          <t>09-03-2026 09:28:48</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>09-03-2026 11:56:48</t>
+          <t>09-03-2026 09:41:11</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3405,7 +3397,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>09-03-2026 11:55:41</t>
+          <t>09-03-2026 09:35:16</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3425,22 +3417,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26070523005070004989</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>IVAN ALBERTO NUÑEZ SANCHEZ</t>
-        </is>
-      </c>
+          <t>26070523002390004979</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3457,12 +3441,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>348706</t>
+          <t>348288</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90871</t>
+          <t>90453</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3472,17 +3456,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DANIELA</t>
+          <t>HECTOR SAUL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NORIS</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3492,43 +3476,47 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6634309881</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6642192653</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>9562</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>27-12-1998</t>
+          <t>12-08-2001</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>DANIELA.NORIS27@GMAIL.COM</t>
+          <t>HECTOR.SMD1281@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>05-03-2026 14:35:45</t>
+          <t>03-03-2026 20:48:38</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3538,21 +3526,29 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>06-03-2026 15:02:17</t>
+          <t>03-03-2026 20:51:55</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:51:17</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3560,7 +3556,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26070522951760004878</t>
+          <t>26070522861580004626</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3572,24 +3568,24 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>348288</t>
+          <t>349460</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90453</t>
+          <t>91625</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3599,17 +3595,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>HECTOR SAUL</t>
+          <t>ITZEL GABRIELA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3619,67 +3615,67 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6642192653</t>
+          <t>6641717434</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>12-08-2001</t>
+          <t>11-05-2000</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>HECTOR.SMD1281@GMAIL.COM</t>
+          <t>CORTEZITZEL886@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>03-03-2026 20:48:38</t>
+          <t>09-03-2026 14:46:28</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>03-03-2026 20:51:55</t>
+          <t>09-03-2026 14:49:57</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>03-03-2026 20:51:17</t>
+          <t>09-03-2026 14:49:23</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3699,36 +3695,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26070522861580004626</t>
+          <t>26070523009930005018</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>348574</t>
+          <t>349760</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90739</t>
+          <t>91925</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3738,27 +3734,27 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BLANCA ESTELA</t>
+          <t>YURI</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6643759766</t>
+          <t>6199881225</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3769,17 +3765,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>03-10-1970</t>
+          <t>25-12-1988</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>PENDIRNEJDJK@GMAIL.COM</t>
+          <t>YURIGONZALEZ2506@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>04-03-2026 18:43:05</t>
+          <t>10-03-2026 08:00:07</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3804,12 +3800,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>04-03-2026 20:42:43</t>
+          <t>12-03-2026 08:03:33</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>11-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3826,15 +3822,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26070522899730004730</t>
+          <t>26070523117120005330</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>899</t>
@@ -3842,24 +3842,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>348289</t>
+          <t>348579</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>90744</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3869,17 +3869,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DULCE KARINA </t>
+          <t xml:space="preserve">OLIVIA </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>LIZARRAGA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6647633676</t>
+          <t>6673906676</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>VCV</t>
+          <t>REFDC</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3904,52 +3904,52 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>09-03-2002</t>
+          <t>04-06-2010</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>DULCEKARINAIBAEEALEYVA@GMAIL.COM</t>
+          <t>PARRAOLIVIA459@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>03-03-2026 20:49:06</t>
+          <t>04-03-2026 18:53:57</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>03-03-2026 20:54:36</t>
+          <t>09-03-2026 17:57:17</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>03-03-2026 20:54:05</t>
+          <t>09-03-2026 17:56:24</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3969,19 +3969,27 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26070522861670004628</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26070523020030005043</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>KIMBERLY MICHEL ROMERO  BRITO</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3993,12 +4001,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>348769</t>
+          <t>349445</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90934</t>
+          <t>91610</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4008,17 +4016,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>ALMA JUDITH</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>URIARTE</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4028,33 +4036,33 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6674212830</t>
+          <t>6645194747</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>23-06-2010</t>
+          <t>17-04-1993</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>DAVID.URIARTEP23@GMAIL.COM</t>
+          <t>JUDITH.LG.0493@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>05-03-2026 17:34:58</t>
+          <t>09-03-2026 14:20:45</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4064,17 +4072,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>09-03-2026 17:49:12</t>
+          <t>09-03-2026 14:21:56</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4096,18 +4104,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26070523019250005037</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26070523008840004998</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4124,12 +4128,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>349335</t>
+          <t>349637</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>91500</t>
+          <t>91802</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4139,17 +4143,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ANGEL IGNACIO</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>PRECIADO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4159,12 +4163,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6631126650</t>
+          <t>6645943269</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C DIRECCION DEL TRABAJO 15700</t>
+          <t>PRIV BOURGES</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4174,42 +4178,42 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>07-02-2002</t>
+          <t>23-01-2002</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>IGNACIOCASTRO124@GMAIL.COM</t>
+          <t>SEBASTIANPRECIADOAGUILAR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>09-03-2026 09:28:48</t>
+          <t>09-03-2026 18:57:23</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>09-03-2026 09:41:11</t>
+          <t>09-03-2026 19:03:51</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4219,7 +4223,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>09-03-2026 09:35:16</t>
+          <t>09-03-2026 19:03:12</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4239,36 +4243,36 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26070523002390004979</t>
+          <t>26070523025520005064</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>349460</t>
+          <t>348600</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>91625</t>
+          <t>90765</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4278,17 +4282,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ITZEL GABRIELA</t>
+          <t>ALICIA ALEJANDRA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t>DELGADILLO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>NEVAREZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4298,12 +4302,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6641717434</t>
+          <t>6642840914</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PANFILO NATERA 5818</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4313,17 +4317,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>11-05-2000</t>
+          <t>18-05-1987</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CORTEZITZEL886@GMAIL.COM</t>
+          <t>ALEJA92_64@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-03-2026 14:46:28</t>
+          <t>04-03-2026 20:39:25</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4348,7 +4352,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>09-03-2026 14:49:57</t>
+          <t>09-03-2026 11:56:48</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4358,7 +4362,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>09-03-2026 14:49:23</t>
+          <t>09-03-2026 11:55:41</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4378,11 +4382,19 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26070523009930005018</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+          <t>26070523005070004989</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>IVAN ALBERTO NUÑEZ SANCHEZ</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>649</t>
@@ -4390,24 +4402,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>348579</t>
+          <t>348769</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90744</t>
+          <t>90934</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4417,19 +4429,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVIA </t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>URIARTE</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>PARRA</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>LIZARRAGA</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>52</t>
@@ -4437,57 +4449,53 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6673906676</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>REFDC</t>
-        </is>
-      </c>
+          <t>6674212830</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>04-06-2010</t>
+          <t>23-06-2010</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>PARRAOLIVIA459@GMAIL.COM</t>
+          <t>DAVID.URIARTEP23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>04-03-2026 18:53:57</t>
+          <t>05-03-2026 17:34:58</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-03-2026 17:57:17</t>
+          <t>09-03-2026 17:49:12</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4495,21 +4503,13 @@
           <t>08-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>09-03-2026 17:56:24</t>
-        </is>
-      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4517,44 +4517,40 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26070523020030005043</t>
+          <t>26070523019250005037</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>KIMBERLY MICHEL ROMERO  BRITO</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>349440</t>
+          <t>347797</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>91605</t>
+          <t>89962</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4564,17 +4560,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FERNANDA</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SANTILLANES</t>
+          <t>BARRADAS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4584,10 +4580,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6634037703</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>6561309595</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4595,32 +4595,32 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>26-09-2009</t>
+          <t>25-03-1994</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>FERNANDA.ESPINOZA2627@GMAIL.COM</t>
+          <t>ELIZABETH.CBARRADAS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-03-2026 14:13:43</t>
+          <t>02-03-2026 18:11:42</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4630,21 +4630,29 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>09-03-2026 14:14:23</t>
+          <t>02-03-2026 18:15:07</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:14:46</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4652,7 +4660,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26070523008620004997</t>
+          <t>26070522810970004458</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4664,24 +4672,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>349760</t>
+          <t>349840</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>91925</t>
+          <t>92005</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4691,53 +4699,53 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>YURI</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ROMO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>BARAJAS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6199881225</t>
+          <t>6642252510</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>25-12-1988</t>
+          <t>29-10-1983</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>YURIGONZALEZ2506@ICLOUD.COM</t>
+          <t>ROMOBARAJASCARLOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10-03-2026 08:00:07</t>
+          <t>10-03-2026 13:49:19</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -4747,22 +4755,22 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>12-03-2026 08:03:33</t>
+          <t>19-03-2026 14:02:57</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
+          <t>18-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -4779,22 +4787,18 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26070523117120005330</t>
+          <t>26070523328620005847</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>TOMAS HERNANDEZ MARTINEZ</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4811,12 +4815,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>349157</t>
+          <t>349931</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>91322</t>
+          <t>92096</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4826,17 +4830,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GISELA</t>
+          <t>ESPERANZA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>ARAGON</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PRUDENTE</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4846,12 +4850,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6648198159</t>
+          <t>6643704380</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>C DE LOS MANZA</t>
+          <t>RES</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4861,52 +4865,52 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>08-01-1999</t>
+          <t>20-02-1972</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>GISELA.PRUDENTE.2022@GMAIL.COM</t>
+          <t>ESPE2020@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>07-03-2026 13:53:28</t>
+          <t>10-03-2026 18:06:52</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>07-03-2026 13:59:02</t>
+          <t>10-03-2026 18:25:11</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>07-03-2026 13:58:20</t>
+          <t>10-03-2026 18:14:53</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4916,7 +4920,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4926,14 +4930,14 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26070522975890004938</t>
+          <t>26070523063930005184</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4950,12 +4954,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>349249</t>
+          <t>349735</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>91414</t>
+          <t>91900</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4965,17 +4969,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EMILIANO</t>
+          <t>RAFAEL LEONARDO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>GASCA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>OSORIO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4985,14 +4989,10 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6642382430</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>KMKL</t>
-        </is>
-      </c>
+          <t>6647518542</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5000,32 +5000,32 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>16-08-2009</t>
+          <t>11-10-1996</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>EMILLIANOAGUILARCONTRERAS@GMAIL.COM</t>
+          <t>LEOGASCA158@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>08-03-2026 13:14:38</t>
+          <t>09-03-2026 21:20:58</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -5035,29 +5035,21 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>08-03-2026 13:19:15</t>
+          <t>09-03-2026 21:23:29</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>07-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>08-03-2026 13:18:35</t>
-        </is>
-      </c>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5065,7 +5057,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26070522986890004946</t>
+          <t>26070523033690005092</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -5077,24 +5069,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>349711</t>
+          <t>349517</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>91876</t>
+          <t>91682</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5104,17 +5096,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JUAN</t>
+          <t>CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ALVA</t>
+          <t>YAÑEZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5124,12 +5116,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6644383790</t>
+          <t>2382522288</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>REFVC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5139,22 +5131,22 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>10-03-1984</t>
+          <t>15-04-2003</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>JUAN_CARRILLO85@HOTMAIL.COM</t>
+          <t>CARLOS_RY@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-03-2026 20:15:18</t>
+          <t>09-03-2026 16:50:32</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -5164,27 +5156,27 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>13-03-2026 21:19:57</t>
+          <t>30-03-2026 16:50:53</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>12-04-2026 23:59:59</t>
+          <t>29-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>13-03-2026 21:19:22</t>
+          <t>30-03-2026 16:50:17</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5194,7 +5186,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5204,7 +5196,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26070523165650005470</t>
+          <t>26070523635470006651</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -5215,7 +5207,7 @@
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5232,12 +5224,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>349929</t>
+          <t>350158</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>92094</t>
+          <t>92323</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5247,17 +5239,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PAOLA YANELY</t>
+          <t>STEVEN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ARMENTA</t>
+          <t>LIU</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>HEU</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5267,14 +5259,10 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6643308000</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
+          <t>6646935482</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5282,64 +5270,56 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>27-04-1981</t>
+          <t>11-03-2011</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>LIAYOMARAPAO1503@GMAIL.COM</t>
+          <t>STEVENLIU110327@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10-03-2026 18:05:51</t>
+          <t>11-03-2026 16:50:12</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>10-03-2026 18:12:15</t>
+          <t>18-03-2026 16:08:45</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>10-03-2026 18:10:50</t>
-        </is>
-      </c>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5347,36 +5327,40 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26070523062780005181</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
+          <t>26070523295830005778</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Brayan Guadalupe Velazquez Zunun</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>349445</t>
+          <t>349157</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>91610</t>
+          <t>91322</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5386,17 +5370,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ALMA JUDITH</t>
+          <t>GISELA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>PRUDENTE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5406,10 +5390,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6645194747</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6648198159</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>C DE LOS MANZA</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5417,56 +5405,64 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>17-04-1993</t>
+          <t>08-01-1999</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>JUDITH.LG.0493@GMAIL.COM</t>
+          <t>GISELA.PRUDENTE.2022@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>09-03-2026 14:20:45</t>
+          <t>07-03-2026 13:53:28</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>09-03-2026 14:21:56</t>
+          <t>07-03-2026 13:59:02</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:58:20</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5474,36 +5470,36 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26070523008840004998</t>
+          <t>26070522975890004938</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>349637</t>
+          <t>350660</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>91802</t>
+          <t>92824</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5513,17 +5509,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>DIONE XARENY</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PRECIADO</t>
+          <t>AVENDAÑO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>ROBLEZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5533,79 +5529,63 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6645943269</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>PRIV BOURGES</t>
-        </is>
-      </c>
+          <t>6646141928</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>23-01-2002</t>
+          <t>28-09-2000</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>SEBASTIANPRECIADOAGUILAR@GMAIL.COM</t>
+          <t>ROBLEZCYNTHIA12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>09-03-2026 18:57:23</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-03-2026 18:41:24</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>09-03-2026 19:03:51</t>
+          <t>13-03-2026 18:45:31</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>09-03-2026 19:03:12</t>
-        </is>
-      </c>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5613,14 +5593,14 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26070523025520005064</t>
+          <t>26070523161560005460</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5637,12 +5617,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>349840</t>
+          <t>349711</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>92005</t>
+          <t>91876</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5652,17 +5632,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>JUAN</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ROMO</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BARAJAS</t>
+          <t>ALVA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5672,10 +5652,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6642252510</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6644383790</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>REFVC</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5683,32 +5667,32 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>29-10-1983</t>
+          <t>10-03-1984</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ROMOBARAJASCARLOS@GMAIL.COM</t>
+          <t>JUAN_CARRILLO85@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>10-03-2026 13:49:19</t>
+          <t>09-03-2026 20:15:18</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -5718,21 +5702,29 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>19-03-2026 14:02:57</t>
+          <t>13-03-2026 21:19:57</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>13-03-2026 21:19:22</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5740,7 +5732,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26070523328620005847</t>
+          <t>26070523165650005470</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5756,24 +5748,24 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>349931</t>
+          <t>350608</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>92096</t>
+          <t>92772</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5783,17 +5775,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ESPERANZA</t>
+          <t>BRYAN</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ARAGON</t>
+          <t>MELENDEZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>HIDALGO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5803,67 +5795,67 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6643704380</t>
+          <t>6634041120</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>20-02-1972</t>
+          <t>22-04-2004</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ESPE2020@HOTMAIL.COM</t>
+          <t>ORK4N080@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>10-03-2026 18:06:52</t>
+          <t>13-03-2026 16:15:29</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>10-03-2026 18:25:11</t>
+          <t>13-03-2026 16:18:46</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>12-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>10-03-2026 18:14:53</t>
+          <t>13-03-2026 16:18:13</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5873,7 +5865,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5883,14 +5875,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26070523063930005184</t>
+          <t>26070523156120005441</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -6034,12 +6026,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>349735</t>
+          <t>349929</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>91900</t>
+          <t>92094</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6049,17 +6041,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>RAFAEL LEONARDO</t>
+          <t>PAOLA YANELY</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GASCA</t>
+          <t>ARMENTA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>OSORIO</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6069,67 +6061,79 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6647518542</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>6643308000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>11-10-1996</t>
+          <t>27-04-1981</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>LEOGASCA158@GMAIL.COM</t>
+          <t>LIAYOMARAPAO1503@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>09-03-2026 21:20:58</t>
+          <t>10-03-2026 18:05:51</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>09-03-2026 21:23:29</t>
+          <t>10-03-2026 18:12:15</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr"/>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:10:50</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6137,36 +6141,36 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26070523033690005092</t>
+          <t>26070523062780005181</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>350349</t>
+          <t>349956</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>92513</t>
+          <t>92121</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6176,27 +6180,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KARINA VANESSA</t>
+          <t>JULIANA SARAI</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GAYTAN</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>VERDUGO</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6198165722</t>
+          <t>6642204712</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6207,22 +6211,22 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>27-11-1996</t>
+          <t>09-07-1984</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>KARINA.GAYTAN11271996@GMAIL.COM</t>
+          <t>J.CRUZC@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>12-03-2026 14:45:22</t>
+          <t>10-03-2026 18:36:28</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -6232,22 +6236,22 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>16-03-2026 19:08:40</t>
+          <t>10-03-2026 18:37:53</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -6264,14 +6268,14 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26070523232220005584</t>
+          <t>26070523064960005192</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -6288,12 +6292,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>350158</t>
+          <t>349249</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>92323</t>
+          <t>91414</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6303,17 +6307,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>STEVEN</t>
+          <t>EMILIANO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LIU</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>HEU</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6323,43 +6327,47 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6646935482</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>6642382430</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>KMKL</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>11-03-2011</t>
+          <t>16-08-2009</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>STEVENLIU110327@ICLOUD.COM</t>
+          <t>EMILLIANOAGUILARCONTRERAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>11-03-2026 16:50:12</t>
+          <t>08-03-2026 13:14:38</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6369,21 +6377,29 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>18-03-2026 16:08:45</t>
+          <t>08-03-2026 13:19:15</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr"/>
+          <t>07-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>08-03-2026 13:18:35</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6391,14 +6407,10 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26070523295830005778</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26070522986890004946</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
@@ -6407,24 +6419,24 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>350660</t>
+          <t>351354</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>92824</t>
+          <t>93518</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6434,19 +6446,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DIONE XARENY</t>
+          <t xml:space="preserve">EVA SAMANTHA </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>CORNEJO</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>AVENDAÑO</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>ROBLEZ</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>52</t>
@@ -6454,7 +6466,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6646141928</t>
+          <t>6634424337</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6465,20 +6477,24 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>28-09-2000</t>
+          <t>22-09-2006</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ROBLEZCYNTHIA12@GMAIL.COM</t>
+          <t>SAMANTHA.PRIV76@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>13-03-2026 18:41:24</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>16-03-2026 19:52:38</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -6486,28 +6502,28 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>13-03-2026 18:45:31</t>
+          <t>16-03-2026 19:53:37</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>12-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V45" t="inlineStr"/>
@@ -6518,36 +6534,36 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26070523161560005460</t>
+          <t>26070523234150005586</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Tania  Toriz Salazar</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>349956</t>
+          <t>348211</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>92121</t>
+          <t>90376</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6557,17 +6573,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JULIANA SARAI</t>
+          <t>OMAR EDUARDO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6577,67 +6593,79 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6642204712</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>5574031355</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>FDC</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>09-07-1984</t>
+          <t>11-10-1986</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>J.CRUZC@OUTLOOK.COM</t>
+          <t>EDU_19TJ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>10-03-2026 18:36:28</t>
+          <t>03-03-2026 18:08:17</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>10-03-2026 18:37:53</t>
+          <t>03-03-2026 18:11:01</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:10:30</t>
+        </is>
+      </c>
       <c r="U46" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6645,36 +6673,36 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26070523064960005192</t>
+          <t>26070522853820004601</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>350608</t>
+          <t>348212</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>92772</t>
+          <t>90377</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6684,17 +6712,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BRYAN</t>
+          <t>PABLO JAVIER</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MELENDEZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6704,12 +6732,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6634041120</t>
+          <t>6643475625</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6719,17 +6747,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>22-04-2004</t>
+          <t>05-04-2005</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ORK4N080@GMAIL.COM</t>
+          <t>PABLOJDIAZ9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>13-03-2026 16:15:29</t>
+          <t>03-03-2026 18:08:31</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6754,17 +6782,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>13-03-2026 16:18:46</t>
+          <t>03-03-2026 18:12:47</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>12-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>13-03-2026 16:18:13</t>
+          <t>03-03-2026 18:12:21</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6784,7 +6812,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26070523156120005441</t>
+          <t>26070522853900004602</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6947,12 +6975,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>351349</t>
+          <t>352018</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>93513</t>
+          <t>94182</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6962,17 +6990,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MAYTEE IRASEMA</t>
+          <t>MARIA GUADALUPE</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>MATUZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AVENDAÑO</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6982,14 +7010,10 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6648958715</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>HJG</t>
-        </is>
-      </c>
+          <t>6442219951</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6997,60 +7021,56 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>13-10-1999</t>
+          <t>08-09-1995</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>MAYTEE.MUNOZ@OUTLOOK.ES</t>
+          <t>MATUZ2812@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>16-03-2026 19:47:45</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>18-03-2026 21:13:15</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>16-03-2026 20:32:12</t>
+          <t>18-03-2026 21:14:08</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>16-03-2026 19:50:20</t>
-        </is>
-      </c>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
           <t>2</t>
         </is>
       </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7058,14 +7078,14 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26070523235290005589</t>
+          <t>26070523311000005823</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -7082,12 +7102,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>351025</t>
+          <t>351349</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>93189</t>
+          <t>93513</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7097,17 +7117,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">HECTOR HELIO </t>
+          <t>MAYTEE IRASEMA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>AVENDAÑO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7117,39 +7137,35 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6642926962</t>
+          <t>6648958715</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>HJG</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>12-09-1981</t>
+          <t>13-10-1999</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>HECSAN@GMAIL.COM</t>
+          <t>MAYTEE.MUNOZ@OUTLOOK.ES</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>16-03-2026 09:21:21</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>16-03-2026 19:47:45</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>No Forzoso</t>
@@ -7157,17 +7173,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>16-03-2026 09:30:45</t>
+          <t>16-03-2026 20:32:12</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -7177,19 +7193,19 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>16-03-2026 09:30:07</t>
+          <t>16-03-2026 19:50:20</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7197,14 +7213,14 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26070523212510005534</t>
+          <t>26070523235290005589</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -7221,12 +7237,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>352018</t>
+          <t>351025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>94182</t>
+          <t>93189</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7236,17 +7252,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MARIA GUADALUPE</t>
+          <t xml:space="preserve">HECTOR HELIO </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MATUZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7256,28 +7272,32 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6442219951</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>6642926962</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>08-09-1995</t>
+          <t>12-09-1981</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>MATUZ2812@GMAIL.COM</t>
+          <t>HECSAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>18-03-2026 21:13:15</t>
+          <t>16-03-2026 09:21:21</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7287,36 +7307,44 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>18-03-2026 21:14:08</t>
+          <t>16-03-2026 09:30:45</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr"/>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>16-03-2026 09:30:07</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7324,36 +7352,36 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26070523311000005823</t>
+          <t>26070523212510005534</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>351354</t>
+          <t>348706</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>93518</t>
+          <t>90871</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7363,17 +7391,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVA SAMANTHA </t>
+          <t>DANIELA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CORNEJO</t>
+          <t>NORIS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AVENDAÑO</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7383,7 +7411,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6634424337</t>
+          <t>6634309881</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7394,22 +7422,22 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>22-09-2006</t>
+          <t>27-12-1998</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>SAMANTHA.PRIV76@GMAIL.COM</t>
+          <t>DANIELA.NORIS27@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>16-03-2026 19:52:38</t>
+          <t>05-03-2026 14:35:45</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -7419,28 +7447,28 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>16-03-2026 19:53:37</t>
+          <t>06-03-2026 15:02:17</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V52" t="inlineStr"/>
@@ -7451,36 +7479,36 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26070523234150005586</t>
+          <t>26070522951760004878</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>351528</t>
+          <t>351509</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>93692</t>
+          <t>93673</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7490,17 +7518,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>ASHLEY LILIANA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BERNAL</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7510,47 +7538,43 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6631044272</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>FTG</t>
-        </is>
-      </c>
+          <t>6644425392</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>05-05-1998</t>
+          <t>13-10-2009</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>LUISBERNAL050598@GMAIL.COM</t>
+          <t>ASHLEYRAMIREZC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>17-03-2026 14:47:29</t>
+          <t>17-03-2026 13:42:53</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -7560,29 +7584,21 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>17-03-2026 14:50:58</t>
+          <t>23-03-2026 13:39:25</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>17-03-2026 14:50:25</t>
-        </is>
-      </c>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7590,11 +7606,19 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26070523255000005652</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
+          <t>26070523426330006068</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>TOMAS HERNANDEZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>549</t>
@@ -7602,7 +7626,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Cesar Ivan Hernandez Garcia</t>
+          <t>Brayan Guadalupe Velazquez Zunun</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7614,12 +7638,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>351531</t>
+          <t>351528</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>93695</t>
+          <t>93692</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7629,17 +7653,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESSY JISSELY </t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BOJORQUEZ</t>
+          <t>BERNAL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BERNAL</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7649,32 +7673,32 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6647268756</t>
+          <t>6631044272</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>FDV</t>
+          <t>FTG</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>02-07-1997</t>
+          <t>05-05-1998</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>JESSY.BOJORQUEZ.B1@GMAIL.COM</t>
+          <t>LUISBERNAL050598@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>17-03-2026 14:54:16</t>
+          <t>17-03-2026 14:47:29</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7699,7 +7723,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>17-03-2026 14:57:05</t>
+          <t>17-03-2026 14:50:58</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -7709,7 +7733,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>17-03-2026 14:56:43</t>
+          <t>17-03-2026 14:50:25</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7729,7 +7753,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26070523255210005653</t>
+          <t>26070523255000005652</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
@@ -7741,10 +7765,1479 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
+          <t>Cesar Ivan Hernandez Garcia</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>351531</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>93695</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JESSY JISSELY </t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>BOJORQUEZ</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>BERNAL</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>6647268756</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>FDV</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>02-07-1997</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>JESSY.BOJORQUEZ.B1@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>17-03-2026 14:54:16</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>17-03-2026 14:57:05</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>17-03-2026 14:56:43</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26070523255210005653</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>352354</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>94518</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PEDRO PASCUAL</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ZEQUEIDA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>6633353274</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>27-03-2005</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>PEDROHERNANDEZZEQUEIDA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>20-03-2026 16:31:25</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>30-03-2026 16:50:53</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26070523635470006651</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>352968</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>95132</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LUIS ROBERTO</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ORTIZ</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>6643664136</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>14-03-1995</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>LUISROBERTORODRIGUEZORTIZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>23-03-2026 20:01:11</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>23-03-2026 20:02:29</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26070523446580006143</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Brenda Tania  Toriz Salazar</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>352692</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>94856</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MIRIAM DENISE</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>MIRANDA</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>VALENZUELA</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>6632321540</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>C TONALA 21523</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>08-07-1983</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>MMIRIAM83@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>23-03-2026 09:53:04</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>24-03-2026 10:30:42</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>24-03-2026 10:29:59</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26070523463160006184</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>352787</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>94951</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SOL ANGEL</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ACOSTA</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>6646037643</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>20-07-1993</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>ACOSTAMORENOSOL2007@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>23-03-2026 15:16:56</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>27-03-2026 15:14:35</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>26-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26070523566100006517</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>KIMBERLY MICHEL ROMERO  BRITO</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>349440</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>91605</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>FERNANDA</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ESPINOZA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SANTILLANES</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6634037703</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>26-09-2009</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>FERNANDA.ESPINOZA2627@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:13:43</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:14:23</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26070523008620004997</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>354217</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>96381</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ASHLEY YAMILETTE</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6644917712</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>19-01-2002</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>ASHLEY19YAMILETTE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>30-03-2026 14:15:34</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>30-03-2026 14:16:19</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26070523629530006622</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>350349</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>92513</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>KARINA VANESSA</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>GAYTAN</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>VERDUGO</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6198165722</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>27-11-1996</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>KARINA.GAYTAN11271996@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:45:22</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:08:40</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26070523232220005584</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>351433</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>93597</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ABIGAIL</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>MONTOYA</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>VÁZQUEZ</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6682210986</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>AV E TRIGARANTE 8102 C</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>10-12-1999</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>VAZQUEZABBY1122@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:04:44</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>20-03-2026 10:28:47</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>19-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>20-03-2026 10:27:48</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26070523361260005940</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Yadira Polo</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>351609</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>93773</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BRENDA</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>MELERO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>RAMÍREZ</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6642044862</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>13-07-1982</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>MELEROB4916@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:54:17</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>20-03-2026 19:01:27</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>19-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26070523374110005978</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Brenda Tania  Toriz Salazar</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>352958</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>95122</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDGAR FERNANDO </t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>NAVARRO</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6631070792</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>19-08-1994</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>FERNANDONAVARRO7777777@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>23-03-2026 19:45:32</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>23-03-2026 19:58:43</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>23-03-2026 19:57:42</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26070523446350006141</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>
